--- a/Data/Figure2/Weight/Weight.xlsx
+++ b/Data/Figure2/Weight/Weight.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure2\Weight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1E2B41E-0364-4FBE-8255-0235A6F7DCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70355967-48FF-4274-AA88-A7E4A3DC2E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="79">
   <si>
     <t>Mouse</t>
   </si>
@@ -214,6 +214,51 @@
   </si>
   <si>
     <t>M5-C5</t>
+  </si>
+  <si>
+    <t>21M1</t>
+  </si>
+  <si>
+    <t>21M2</t>
+  </si>
+  <si>
+    <t>21M3</t>
+  </si>
+  <si>
+    <t>21M4</t>
+  </si>
+  <si>
+    <t>30M1</t>
+  </si>
+  <si>
+    <t>30M2</t>
+  </si>
+  <si>
+    <t>30M3</t>
+  </si>
+  <si>
+    <t>64M1</t>
+  </si>
+  <si>
+    <t>64M2</t>
+  </si>
+  <si>
+    <t>64M3</t>
+  </si>
+  <si>
+    <t>64M4</t>
+  </si>
+  <si>
+    <t>66M1</t>
+  </si>
+  <si>
+    <t>66M3</t>
+  </si>
+  <si>
+    <t>76M1</t>
+  </si>
+  <si>
+    <t>76M2</t>
   </si>
 </sst>
 </file>
@@ -4054,7 +4099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E347"/>
+  <dimension ref="A1:E453"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
@@ -9956,6 +10001,1808 @@
         <v>6</v>
       </c>
       <c r="E347" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>64</v>
+      </c>
+      <c r="B348">
+        <v>24.7</v>
+      </c>
+      <c r="C348" t="s">
+        <v>13</v>
+      </c>
+      <c r="D348" t="s">
+        <v>6</v>
+      </c>
+      <c r="E348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>64</v>
+      </c>
+      <c r="B349">
+        <v>28.3</v>
+      </c>
+      <c r="C349" t="s">
+        <v>13</v>
+      </c>
+      <c r="D349" t="s">
+        <v>6</v>
+      </c>
+      <c r="E349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>64</v>
+      </c>
+      <c r="B350">
+        <v>29.3</v>
+      </c>
+      <c r="C350" t="s">
+        <v>13</v>
+      </c>
+      <c r="D350" t="s">
+        <v>6</v>
+      </c>
+      <c r="E350">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>64</v>
+      </c>
+      <c r="B351">
+        <v>31</v>
+      </c>
+      <c r="C351" t="s">
+        <v>13</v>
+      </c>
+      <c r="D351" t="s">
+        <v>6</v>
+      </c>
+      <c r="E351">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>64</v>
+      </c>
+      <c r="B352">
+        <v>31.3</v>
+      </c>
+      <c r="C352" t="s">
+        <v>13</v>
+      </c>
+      <c r="D352" t="s">
+        <v>6</v>
+      </c>
+      <c r="E352">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>64</v>
+      </c>
+      <c r="B353">
+        <v>31.1</v>
+      </c>
+      <c r="C353" t="s">
+        <v>13</v>
+      </c>
+      <c r="D353" t="s">
+        <v>6</v>
+      </c>
+      <c r="E353">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>64</v>
+      </c>
+      <c r="B354">
+        <v>35.5</v>
+      </c>
+      <c r="C354" t="s">
+        <v>13</v>
+      </c>
+      <c r="D354" t="s">
+        <v>6</v>
+      </c>
+      <c r="E354">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>65</v>
+      </c>
+      <c r="B355">
+        <v>26.6</v>
+      </c>
+      <c r="C355" t="s">
+        <v>13</v>
+      </c>
+      <c r="D355" t="s">
+        <v>6</v>
+      </c>
+      <c r="E355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>65</v>
+      </c>
+      <c r="B356">
+        <v>29.4</v>
+      </c>
+      <c r="C356" t="s">
+        <v>13</v>
+      </c>
+      <c r="D356" t="s">
+        <v>6</v>
+      </c>
+      <c r="E356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>65</v>
+      </c>
+      <c r="B357">
+        <v>29.1</v>
+      </c>
+      <c r="C357" t="s">
+        <v>13</v>
+      </c>
+      <c r="D357" t="s">
+        <v>6</v>
+      </c>
+      <c r="E357">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>65</v>
+      </c>
+      <c r="B358">
+        <v>31</v>
+      </c>
+      <c r="C358" t="s">
+        <v>13</v>
+      </c>
+      <c r="D358" t="s">
+        <v>6</v>
+      </c>
+      <c r="E358">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>65</v>
+      </c>
+      <c r="B359">
+        <v>30.8</v>
+      </c>
+      <c r="C359" t="s">
+        <v>13</v>
+      </c>
+      <c r="D359" t="s">
+        <v>6</v>
+      </c>
+      <c r="E359">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>65</v>
+      </c>
+      <c r="B360">
+        <v>30.2</v>
+      </c>
+      <c r="C360" t="s">
+        <v>13</v>
+      </c>
+      <c r="D360" t="s">
+        <v>6</v>
+      </c>
+      <c r="E360">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>65</v>
+      </c>
+      <c r="B361">
+        <v>31.3</v>
+      </c>
+      <c r="C361" t="s">
+        <v>13</v>
+      </c>
+      <c r="D361" t="s">
+        <v>6</v>
+      </c>
+      <c r="E361">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>66</v>
+      </c>
+      <c r="B362">
+        <v>26.9</v>
+      </c>
+      <c r="C362" t="s">
+        <v>13</v>
+      </c>
+      <c r="D362" t="s">
+        <v>6</v>
+      </c>
+      <c r="E362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>66</v>
+      </c>
+      <c r="B363">
+        <v>29.3</v>
+      </c>
+      <c r="C363" t="s">
+        <v>13</v>
+      </c>
+      <c r="D363" t="s">
+        <v>6</v>
+      </c>
+      <c r="E363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>66</v>
+      </c>
+      <c r="B364">
+        <v>29.9</v>
+      </c>
+      <c r="C364" t="s">
+        <v>13</v>
+      </c>
+      <c r="D364" t="s">
+        <v>6</v>
+      </c>
+      <c r="E364">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>66</v>
+      </c>
+      <c r="B365">
+        <v>30.8</v>
+      </c>
+      <c r="C365" t="s">
+        <v>13</v>
+      </c>
+      <c r="D365" t="s">
+        <v>6</v>
+      </c>
+      <c r="E365">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>67</v>
+      </c>
+      <c r="B366">
+        <v>26.9</v>
+      </c>
+      <c r="C366" t="s">
+        <v>13</v>
+      </c>
+      <c r="D366" t="s">
+        <v>6</v>
+      </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>67</v>
+      </c>
+      <c r="B367">
+        <v>29.3</v>
+      </c>
+      <c r="C367" t="s">
+        <v>13</v>
+      </c>
+      <c r="D367" t="s">
+        <v>6</v>
+      </c>
+      <c r="E367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>67</v>
+      </c>
+      <c r="B368">
+        <v>29.9</v>
+      </c>
+      <c r="C368" t="s">
+        <v>13</v>
+      </c>
+      <c r="D368" t="s">
+        <v>6</v>
+      </c>
+      <c r="E368">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>67</v>
+      </c>
+      <c r="B369">
+        <v>29.9</v>
+      </c>
+      <c r="C369" t="s">
+        <v>13</v>
+      </c>
+      <c r="D369" t="s">
+        <v>6</v>
+      </c>
+      <c r="E369">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>67</v>
+      </c>
+      <c r="B370">
+        <v>31.9</v>
+      </c>
+      <c r="C370" t="s">
+        <v>13</v>
+      </c>
+      <c r="D370" t="s">
+        <v>6</v>
+      </c>
+      <c r="E370">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>67</v>
+      </c>
+      <c r="B371">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="C371" t="s">
+        <v>13</v>
+      </c>
+      <c r="D371" t="s">
+        <v>6</v>
+      </c>
+      <c r="E371">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>67</v>
+      </c>
+      <c r="B372">
+        <v>35</v>
+      </c>
+      <c r="C372" t="s">
+        <v>13</v>
+      </c>
+      <c r="D372" t="s">
+        <v>6</v>
+      </c>
+      <c r="E372">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>68</v>
+      </c>
+      <c r="B373">
+        <v>27</v>
+      </c>
+      <c r="C373" t="s">
+        <v>13</v>
+      </c>
+      <c r="D373" t="s">
+        <v>25</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>68</v>
+      </c>
+      <c r="B374">
+        <v>26.9</v>
+      </c>
+      <c r="C374" t="s">
+        <v>13</v>
+      </c>
+      <c r="D374" t="s">
+        <v>25</v>
+      </c>
+      <c r="E374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>68</v>
+      </c>
+      <c r="B375">
+        <v>26</v>
+      </c>
+      <c r="C375" t="s">
+        <v>13</v>
+      </c>
+      <c r="D375" t="s">
+        <v>25</v>
+      </c>
+      <c r="E375">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>68</v>
+      </c>
+      <c r="B376">
+        <v>26.9</v>
+      </c>
+      <c r="C376" t="s">
+        <v>13</v>
+      </c>
+      <c r="D376" t="s">
+        <v>25</v>
+      </c>
+      <c r="E376">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>68</v>
+      </c>
+      <c r="B377">
+        <v>25.7</v>
+      </c>
+      <c r="C377" t="s">
+        <v>13</v>
+      </c>
+      <c r="D377" t="s">
+        <v>25</v>
+      </c>
+      <c r="E377">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>68</v>
+      </c>
+      <c r="B378">
+        <v>25.7</v>
+      </c>
+      <c r="C378" t="s">
+        <v>13</v>
+      </c>
+      <c r="D378" t="s">
+        <v>25</v>
+      </c>
+      <c r="E378">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>68</v>
+      </c>
+      <c r="B379">
+        <v>27</v>
+      </c>
+      <c r="C379" t="s">
+        <v>13</v>
+      </c>
+      <c r="D379" t="s">
+        <v>25</v>
+      </c>
+      <c r="E379">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>69</v>
+      </c>
+      <c r="B380">
+        <v>26.5</v>
+      </c>
+      <c r="C380" t="s">
+        <v>13</v>
+      </c>
+      <c r="D380" t="s">
+        <v>25</v>
+      </c>
+      <c r="E380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>69</v>
+      </c>
+      <c r="B381">
+        <v>28.5</v>
+      </c>
+      <c r="C381" t="s">
+        <v>13</v>
+      </c>
+      <c r="D381" t="s">
+        <v>25</v>
+      </c>
+      <c r="E381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>69</v>
+      </c>
+      <c r="B382">
+        <v>29</v>
+      </c>
+      <c r="C382" t="s">
+        <v>13</v>
+      </c>
+      <c r="D382" t="s">
+        <v>25</v>
+      </c>
+      <c r="E382">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>69</v>
+      </c>
+      <c r="B383">
+        <v>28.5</v>
+      </c>
+      <c r="C383" t="s">
+        <v>13</v>
+      </c>
+      <c r="D383" t="s">
+        <v>25</v>
+      </c>
+      <c r="E383">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>69</v>
+      </c>
+      <c r="B384">
+        <v>28.5</v>
+      </c>
+      <c r="C384" t="s">
+        <v>13</v>
+      </c>
+      <c r="D384" t="s">
+        <v>25</v>
+      </c>
+      <c r="E384">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>69</v>
+      </c>
+      <c r="B385">
+        <v>28.5</v>
+      </c>
+      <c r="C385" t="s">
+        <v>13</v>
+      </c>
+      <c r="D385" t="s">
+        <v>25</v>
+      </c>
+      <c r="E385">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>69</v>
+      </c>
+      <c r="B386">
+        <v>29.1</v>
+      </c>
+      <c r="C386" t="s">
+        <v>13</v>
+      </c>
+      <c r="D386" t="s">
+        <v>25</v>
+      </c>
+      <c r="E386">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>70</v>
+      </c>
+      <c r="B387">
+        <v>28.9</v>
+      </c>
+      <c r="C387" t="s">
+        <v>13</v>
+      </c>
+      <c r="D387" t="s">
+        <v>25</v>
+      </c>
+      <c r="E387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>70</v>
+      </c>
+      <c r="B388">
+        <v>27.3</v>
+      </c>
+      <c r="C388" t="s">
+        <v>13</v>
+      </c>
+      <c r="D388" t="s">
+        <v>25</v>
+      </c>
+      <c r="E388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>70</v>
+      </c>
+      <c r="B389">
+        <v>29</v>
+      </c>
+      <c r="C389" t="s">
+        <v>13</v>
+      </c>
+      <c r="D389" t="s">
+        <v>25</v>
+      </c>
+      <c r="E389">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>70</v>
+      </c>
+      <c r="B390">
+        <v>27.3</v>
+      </c>
+      <c r="C390" t="s">
+        <v>13</v>
+      </c>
+      <c r="D390" t="s">
+        <v>25</v>
+      </c>
+      <c r="E390">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>70</v>
+      </c>
+      <c r="B391">
+        <v>29.3</v>
+      </c>
+      <c r="C391" t="s">
+        <v>13</v>
+      </c>
+      <c r="D391" t="s">
+        <v>25</v>
+      </c>
+      <c r="E391">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>70</v>
+      </c>
+      <c r="B392">
+        <v>29.3</v>
+      </c>
+      <c r="C392" t="s">
+        <v>13</v>
+      </c>
+      <c r="D392" t="s">
+        <v>25</v>
+      </c>
+      <c r="E392">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>70</v>
+      </c>
+      <c r="B393">
+        <v>27</v>
+      </c>
+      <c r="C393" t="s">
+        <v>13</v>
+      </c>
+      <c r="D393" t="s">
+        <v>25</v>
+      </c>
+      <c r="E393">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>71</v>
+      </c>
+      <c r="B394">
+        <v>22.5</v>
+      </c>
+      <c r="C394" t="s">
+        <v>13</v>
+      </c>
+      <c r="D394" t="s">
+        <v>6</v>
+      </c>
+      <c r="E394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>71</v>
+      </c>
+      <c r="B395">
+        <v>32.9</v>
+      </c>
+      <c r="C395" t="s">
+        <v>13</v>
+      </c>
+      <c r="D395" t="s">
+        <v>6</v>
+      </c>
+      <c r="E395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>71</v>
+      </c>
+      <c r="B396">
+        <v>28</v>
+      </c>
+      <c r="C396" t="s">
+        <v>13</v>
+      </c>
+      <c r="D396" t="s">
+        <v>6</v>
+      </c>
+      <c r="E396">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>71</v>
+      </c>
+      <c r="B397">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="C397" t="s">
+        <v>13</v>
+      </c>
+      <c r="D397" t="s">
+        <v>6</v>
+      </c>
+      <c r="E397">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>71</v>
+      </c>
+      <c r="B398">
+        <v>31.1</v>
+      </c>
+      <c r="C398" t="s">
+        <v>13</v>
+      </c>
+      <c r="D398" t="s">
+        <v>6</v>
+      </c>
+      <c r="E398">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>71</v>
+      </c>
+      <c r="B399">
+        <v>35</v>
+      </c>
+      <c r="C399" t="s">
+        <v>13</v>
+      </c>
+      <c r="D399" t="s">
+        <v>6</v>
+      </c>
+      <c r="E399">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>71</v>
+      </c>
+      <c r="B400">
+        <v>35</v>
+      </c>
+      <c r="C400" t="s">
+        <v>13</v>
+      </c>
+      <c r="D400" t="s">
+        <v>6</v>
+      </c>
+      <c r="E400">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>71</v>
+      </c>
+      <c r="B401">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="C401" t="s">
+        <v>13</v>
+      </c>
+      <c r="D401" t="s">
+        <v>6</v>
+      </c>
+      <c r="E401">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>72</v>
+      </c>
+      <c r="B402">
+        <v>26.4</v>
+      </c>
+      <c r="C402" t="s">
+        <v>13</v>
+      </c>
+      <c r="D402" t="s">
+        <v>6</v>
+      </c>
+      <c r="E402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>72</v>
+      </c>
+      <c r="B403">
+        <v>31</v>
+      </c>
+      <c r="C403" t="s">
+        <v>13</v>
+      </c>
+      <c r="D403" t="s">
+        <v>6</v>
+      </c>
+      <c r="E403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>72</v>
+      </c>
+      <c r="B404">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="C404" t="s">
+        <v>13</v>
+      </c>
+      <c r="D404" t="s">
+        <v>6</v>
+      </c>
+      <c r="E404">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>72</v>
+      </c>
+      <c r="B405">
+        <v>38</v>
+      </c>
+      <c r="C405" t="s">
+        <v>13</v>
+      </c>
+      <c r="D405" t="s">
+        <v>6</v>
+      </c>
+      <c r="E405">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>72</v>
+      </c>
+      <c r="B406">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="C406" t="s">
+        <v>13</v>
+      </c>
+      <c r="D406" t="s">
+        <v>6</v>
+      </c>
+      <c r="E406">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>72</v>
+      </c>
+      <c r="B407">
+        <v>42.5</v>
+      </c>
+      <c r="C407" t="s">
+        <v>13</v>
+      </c>
+      <c r="D407" t="s">
+        <v>6</v>
+      </c>
+      <c r="E407">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>72</v>
+      </c>
+      <c r="B408">
+        <v>42.5</v>
+      </c>
+      <c r="C408" t="s">
+        <v>13</v>
+      </c>
+      <c r="D408" t="s">
+        <v>6</v>
+      </c>
+      <c r="E408">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>72</v>
+      </c>
+      <c r="B409">
+        <v>44.3</v>
+      </c>
+      <c r="C409" t="s">
+        <v>13</v>
+      </c>
+      <c r="D409" t="s">
+        <v>6</v>
+      </c>
+      <c r="E409">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>73</v>
+      </c>
+      <c r="B410">
+        <v>24.2</v>
+      </c>
+      <c r="C410" t="s">
+        <v>13</v>
+      </c>
+      <c r="D410" t="s">
+        <v>6</v>
+      </c>
+      <c r="E410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>73</v>
+      </c>
+      <c r="B411">
+        <v>34</v>
+      </c>
+      <c r="C411" t="s">
+        <v>13</v>
+      </c>
+      <c r="D411" t="s">
+        <v>6</v>
+      </c>
+      <c r="E411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>73</v>
+      </c>
+      <c r="B412">
+        <v>30.4</v>
+      </c>
+      <c r="C412" t="s">
+        <v>13</v>
+      </c>
+      <c r="D412" t="s">
+        <v>6</v>
+      </c>
+      <c r="E412">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>73</v>
+      </c>
+      <c r="B413">
+        <v>30</v>
+      </c>
+      <c r="C413" t="s">
+        <v>13</v>
+      </c>
+      <c r="D413" t="s">
+        <v>6</v>
+      </c>
+      <c r="E413">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>73</v>
+      </c>
+      <c r="B414">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="C414" t="s">
+        <v>13</v>
+      </c>
+      <c r="D414" t="s">
+        <v>6</v>
+      </c>
+      <c r="E414">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>73</v>
+      </c>
+      <c r="B415">
+        <v>31.8</v>
+      </c>
+      <c r="C415" t="s">
+        <v>13</v>
+      </c>
+      <c r="D415" t="s">
+        <v>6</v>
+      </c>
+      <c r="E415">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>73</v>
+      </c>
+      <c r="B416">
+        <v>31.8</v>
+      </c>
+      <c r="C416" t="s">
+        <v>13</v>
+      </c>
+      <c r="D416" t="s">
+        <v>6</v>
+      </c>
+      <c r="E416">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>73</v>
+      </c>
+      <c r="B417">
+        <v>33</v>
+      </c>
+      <c r="C417" t="s">
+        <v>13</v>
+      </c>
+      <c r="D417" t="s">
+        <v>6</v>
+      </c>
+      <c r="E417">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>74</v>
+      </c>
+      <c r="B418">
+        <v>26.3</v>
+      </c>
+      <c r="C418" t="s">
+        <v>13</v>
+      </c>
+      <c r="D418" t="s">
+        <v>6</v>
+      </c>
+      <c r="E418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>74</v>
+      </c>
+      <c r="B419">
+        <v>31.5</v>
+      </c>
+      <c r="C419" t="s">
+        <v>13</v>
+      </c>
+      <c r="D419" t="s">
+        <v>6</v>
+      </c>
+      <c r="E419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>74</v>
+      </c>
+      <c r="B420">
+        <v>29.8</v>
+      </c>
+      <c r="C420" t="s">
+        <v>13</v>
+      </c>
+      <c r="D420" t="s">
+        <v>6</v>
+      </c>
+      <c r="E420">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>74</v>
+      </c>
+      <c r="B421">
+        <v>30.1</v>
+      </c>
+      <c r="C421" t="s">
+        <v>13</v>
+      </c>
+      <c r="D421" t="s">
+        <v>6</v>
+      </c>
+      <c r="E421">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>74</v>
+      </c>
+      <c r="B422">
+        <v>31</v>
+      </c>
+      <c r="C422" t="s">
+        <v>13</v>
+      </c>
+      <c r="D422" t="s">
+        <v>6</v>
+      </c>
+      <c r="E422">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>74</v>
+      </c>
+      <c r="B423">
+        <v>32.9</v>
+      </c>
+      <c r="C423" t="s">
+        <v>13</v>
+      </c>
+      <c r="D423" t="s">
+        <v>6</v>
+      </c>
+      <c r="E423">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>74</v>
+      </c>
+      <c r="B424">
+        <v>32.9</v>
+      </c>
+      <c r="C424" t="s">
+        <v>13</v>
+      </c>
+      <c r="D424" t="s">
+        <v>6</v>
+      </c>
+      <c r="E424">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>74</v>
+      </c>
+      <c r="B425">
+        <v>35</v>
+      </c>
+      <c r="C425" t="s">
+        <v>13</v>
+      </c>
+      <c r="D425" t="s">
+        <v>6</v>
+      </c>
+      <c r="E425">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>75</v>
+      </c>
+      <c r="B426">
+        <v>21.4</v>
+      </c>
+      <c r="C426" t="s">
+        <v>13</v>
+      </c>
+      <c r="D426" t="s">
+        <v>25</v>
+      </c>
+      <c r="E426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>75</v>
+      </c>
+      <c r="B427">
+        <v>21.4</v>
+      </c>
+      <c r="C427" t="s">
+        <v>13</v>
+      </c>
+      <c r="D427" t="s">
+        <v>25</v>
+      </c>
+      <c r="E427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>75</v>
+      </c>
+      <c r="B428">
+        <v>26.3</v>
+      </c>
+      <c r="C428" t="s">
+        <v>13</v>
+      </c>
+      <c r="D428" t="s">
+        <v>25</v>
+      </c>
+      <c r="E428">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>75</v>
+      </c>
+      <c r="B429">
+        <v>28.5</v>
+      </c>
+      <c r="C429" t="s">
+        <v>13</v>
+      </c>
+      <c r="D429" t="s">
+        <v>25</v>
+      </c>
+      <c r="E429">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>75</v>
+      </c>
+      <c r="B430">
+        <v>28.6</v>
+      </c>
+      <c r="C430" t="s">
+        <v>13</v>
+      </c>
+      <c r="D430" t="s">
+        <v>25</v>
+      </c>
+      <c r="E430">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>75</v>
+      </c>
+      <c r="B431">
+        <v>25.5</v>
+      </c>
+      <c r="C431" t="s">
+        <v>13</v>
+      </c>
+      <c r="D431" t="s">
+        <v>25</v>
+      </c>
+      <c r="E431">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>75</v>
+      </c>
+      <c r="B432">
+        <v>25.7</v>
+      </c>
+      <c r="C432" t="s">
+        <v>13</v>
+      </c>
+      <c r="D432" t="s">
+        <v>25</v>
+      </c>
+      <c r="E432">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>76</v>
+      </c>
+      <c r="B433">
+        <v>22</v>
+      </c>
+      <c r="C433" t="s">
+        <v>13</v>
+      </c>
+      <c r="D433" t="s">
+        <v>25</v>
+      </c>
+      <c r="E433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>76</v>
+      </c>
+      <c r="B434">
+        <v>22</v>
+      </c>
+      <c r="C434" t="s">
+        <v>13</v>
+      </c>
+      <c r="D434" t="s">
+        <v>25</v>
+      </c>
+      <c r="E434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>76</v>
+      </c>
+      <c r="B435">
+        <v>27.6</v>
+      </c>
+      <c r="C435" t="s">
+        <v>13</v>
+      </c>
+      <c r="D435" t="s">
+        <v>25</v>
+      </c>
+      <c r="E435">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>76</v>
+      </c>
+      <c r="B436">
+        <v>27.8</v>
+      </c>
+      <c r="C436" t="s">
+        <v>13</v>
+      </c>
+      <c r="D436" t="s">
+        <v>25</v>
+      </c>
+      <c r="E436">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>76</v>
+      </c>
+      <c r="B437">
+        <v>26</v>
+      </c>
+      <c r="C437" t="s">
+        <v>13</v>
+      </c>
+      <c r="D437" t="s">
+        <v>25</v>
+      </c>
+      <c r="E437">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>76</v>
+      </c>
+      <c r="B438">
+        <v>28.3</v>
+      </c>
+      <c r="C438" t="s">
+        <v>13</v>
+      </c>
+      <c r="D438" t="s">
+        <v>25</v>
+      </c>
+      <c r="E438">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>76</v>
+      </c>
+      <c r="B439">
+        <v>28.3</v>
+      </c>
+      <c r="C439" t="s">
+        <v>13</v>
+      </c>
+      <c r="D439" t="s">
+        <v>25</v>
+      </c>
+      <c r="E439">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>77</v>
+      </c>
+      <c r="B440">
+        <v>26.5</v>
+      </c>
+      <c r="C440" t="s">
+        <v>13</v>
+      </c>
+      <c r="D440" t="s">
+        <v>25</v>
+      </c>
+      <c r="E440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>77</v>
+      </c>
+      <c r="B441">
+        <v>26.5</v>
+      </c>
+      <c r="C441" t="s">
+        <v>13</v>
+      </c>
+      <c r="D441" t="s">
+        <v>25</v>
+      </c>
+      <c r="E441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>77</v>
+      </c>
+      <c r="B442">
+        <v>26.5</v>
+      </c>
+      <c r="C442" t="s">
+        <v>13</v>
+      </c>
+      <c r="D442" t="s">
+        <v>25</v>
+      </c>
+      <c r="E442">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>77</v>
+      </c>
+      <c r="B443">
+        <v>27.2</v>
+      </c>
+      <c r="C443" t="s">
+        <v>13</v>
+      </c>
+      <c r="D443" t="s">
+        <v>25</v>
+      </c>
+      <c r="E443">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>77</v>
+      </c>
+      <c r="B444">
+        <v>27</v>
+      </c>
+      <c r="C444" t="s">
+        <v>13</v>
+      </c>
+      <c r="D444" t="s">
+        <v>25</v>
+      </c>
+      <c r="E444">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>77</v>
+      </c>
+      <c r="B445">
+        <v>27.7</v>
+      </c>
+      <c r="C445" t="s">
+        <v>13</v>
+      </c>
+      <c r="D445" t="s">
+        <v>25</v>
+      </c>
+      <c r="E445">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>77</v>
+      </c>
+      <c r="B446">
+        <v>26.5</v>
+      </c>
+      <c r="C446" t="s">
+        <v>13</v>
+      </c>
+      <c r="D446" t="s">
+        <v>25</v>
+      </c>
+      <c r="E446">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>78</v>
+      </c>
+      <c r="B447">
+        <v>26.3</v>
+      </c>
+      <c r="C447" t="s">
+        <v>13</v>
+      </c>
+      <c r="D447" t="s">
+        <v>25</v>
+      </c>
+      <c r="E447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>78</v>
+      </c>
+      <c r="B448">
+        <v>26.3</v>
+      </c>
+      <c r="C448" t="s">
+        <v>13</v>
+      </c>
+      <c r="D448" t="s">
+        <v>25</v>
+      </c>
+      <c r="E448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>78</v>
+      </c>
+      <c r="B449">
+        <v>26.3</v>
+      </c>
+      <c r="C449" t="s">
+        <v>13</v>
+      </c>
+      <c r="D449" t="s">
+        <v>25</v>
+      </c>
+      <c r="E449">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>78</v>
+      </c>
+      <c r="B450">
+        <v>25.5</v>
+      </c>
+      <c r="C450" t="s">
+        <v>13</v>
+      </c>
+      <c r="D450" t="s">
+        <v>25</v>
+      </c>
+      <c r="E450">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>78</v>
+      </c>
+      <c r="B451">
+        <v>25.8</v>
+      </c>
+      <c r="C451" t="s">
+        <v>13</v>
+      </c>
+      <c r="D451" t="s">
+        <v>25</v>
+      </c>
+      <c r="E451">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>78</v>
+      </c>
+      <c r="B452">
+        <v>26</v>
+      </c>
+      <c r="C452" t="s">
+        <v>13</v>
+      </c>
+      <c r="D452" t="s">
+        <v>25</v>
+      </c>
+      <c r="E452">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>78</v>
+      </c>
+      <c r="B453">
+        <v>26</v>
+      </c>
+      <c r="C453" t="s">
+        <v>13</v>
+      </c>
+      <c r="D453" t="s">
+        <v>25</v>
+      </c>
+      <c r="E453">
         <v>6</v>
       </c>
     </row>

--- a/Data/Figure2/Weight/Weight.xlsx
+++ b/Data/Figure2/Weight/Weight.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure2\Weight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70355967-48FF-4274-AA88-A7E4A3DC2E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE39B7C-3B1A-4199-91CF-A0C8FCBAE4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9057,7 +9057,7 @@
         <v>24</v>
       </c>
       <c r="B292" s="1">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>13</v>
@@ -9066,7 +9066,7 @@
         <v>25</v>
       </c>
       <c r="E292" s="1">
-        <v>0</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -9074,7 +9074,7 @@
         <v>24</v>
       </c>
       <c r="B293" s="1">
-        <v>21.4</v>
+        <v>1</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>13</v>
@@ -9083,7 +9083,7 @@
         <v>25</v>
       </c>
       <c r="E293" s="1">
-        <v>1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -9091,7 +9091,7 @@
         <v>24</v>
       </c>
       <c r="B294" s="1">
-        <v>21.7</v>
+        <v>2</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>13</v>
@@ -9100,7 +9100,7 @@
         <v>25</v>
       </c>
       <c r="E294" s="1">
-        <v>2</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -9108,7 +9108,7 @@
         <v>24</v>
       </c>
       <c r="B295" s="1">
-        <v>21.8</v>
+        <v>3</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>13</v>
@@ -9117,7 +9117,7 @@
         <v>25</v>
       </c>
       <c r="E295" s="1">
-        <v>3</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -9125,7 +9125,7 @@
         <v>24</v>
       </c>
       <c r="B296" s="1">
-        <v>22.8</v>
+        <v>4</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>13</v>
@@ -9134,7 +9134,7 @@
         <v>25</v>
       </c>
       <c r="E296" s="1">
-        <v>4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -9142,7 +9142,7 @@
         <v>24</v>
       </c>
       <c r="B297" s="1">
-        <v>22.8</v>
+        <v>5</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>13</v>
@@ -9151,7 +9151,7 @@
         <v>25</v>
       </c>
       <c r="E297" s="1">
-        <v>5</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -9159,7 +9159,7 @@
         <v>24</v>
       </c>
       <c r="B298" s="1">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>13</v>
@@ -9168,7 +9168,7 @@
         <v>25</v>
       </c>
       <c r="E298" s="1">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -9176,7 +9176,7 @@
         <v>26</v>
       </c>
       <c r="B299" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>13</v>
@@ -9185,7 +9185,7 @@
         <v>25</v>
       </c>
       <c r="E299" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -9193,7 +9193,7 @@
         <v>26</v>
       </c>
       <c r="B300" s="1">
-        <v>24.5</v>
+        <v>1</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>13</v>
@@ -9202,7 +9202,7 @@
         <v>25</v>
       </c>
       <c r="E300" s="1">
-        <v>1</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -9210,7 +9210,7 @@
         <v>26</v>
       </c>
       <c r="B301" s="1">
-        <v>24.4</v>
+        <v>2</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>13</v>
@@ -9219,7 +9219,7 @@
         <v>25</v>
       </c>
       <c r="E301" s="1">
-        <v>2</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -9227,7 +9227,7 @@
         <v>26</v>
       </c>
       <c r="B302" s="1">
-        <v>24.3</v>
+        <v>3</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>13</v>
@@ -9236,7 +9236,7 @@
         <v>25</v>
       </c>
       <c r="E302" s="1">
-        <v>3</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -9244,7 +9244,7 @@
         <v>26</v>
       </c>
       <c r="B303" s="1">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>13</v>
@@ -9253,7 +9253,7 @@
         <v>25</v>
       </c>
       <c r="E303" s="1">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -9261,7 +9261,7 @@
         <v>26</v>
       </c>
       <c r="B304" s="1">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>13</v>
@@ -9270,7 +9270,7 @@
         <v>25</v>
       </c>
       <c r="E304" s="1">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -9278,7 +9278,7 @@
         <v>26</v>
       </c>
       <c r="B305" s="1">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>13</v>
@@ -9287,7 +9287,7 @@
         <v>25</v>
       </c>
       <c r="E305" s="1">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
@@ -9295,7 +9295,7 @@
         <v>27</v>
       </c>
       <c r="B306" s="1">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>13</v>
@@ -9304,7 +9304,7 @@
         <v>25</v>
       </c>
       <c r="E306" s="1">
-        <v>0</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -9312,7 +9312,7 @@
         <v>27</v>
       </c>
       <c r="B307" s="1">
-        <v>25.2</v>
+        <v>1</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>13</v>
@@ -9321,7 +9321,7 @@
         <v>25</v>
       </c>
       <c r="E307" s="1">
-        <v>1</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
@@ -9329,7 +9329,7 @@
         <v>27</v>
       </c>
       <c r="B308" s="1">
-        <v>25.9</v>
+        <v>2</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>13</v>
@@ -9338,7 +9338,7 @@
         <v>25</v>
       </c>
       <c r="E308" s="1">
-        <v>2</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
@@ -9346,7 +9346,7 @@
         <v>27</v>
       </c>
       <c r="B309" s="1">
-        <v>25.8</v>
+        <v>3</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>13</v>
@@ -9355,7 +9355,7 @@
         <v>25</v>
       </c>
       <c r="E309" s="1">
-        <v>3</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
@@ -9363,7 +9363,7 @@
         <v>27</v>
       </c>
       <c r="B310" s="1">
-        <v>26.2</v>
+        <v>4</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>13</v>
@@ -9372,7 +9372,7 @@
         <v>25</v>
       </c>
       <c r="E310" s="1">
-        <v>4</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
@@ -9380,7 +9380,7 @@
         <v>27</v>
       </c>
       <c r="B311" s="1">
-        <v>26.2</v>
+        <v>5</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>13</v>
@@ -9389,7 +9389,7 @@
         <v>25</v>
       </c>
       <c r="E311" s="1">
-        <v>5</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
@@ -9397,7 +9397,7 @@
         <v>27</v>
       </c>
       <c r="B312" s="1">
-        <v>26.2</v>
+        <v>6</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>13</v>
@@ -9406,7 +9406,7 @@
         <v>25</v>
       </c>
       <c r="E312" s="1">
-        <v>6</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
@@ -9414,7 +9414,7 @@
         <v>28</v>
       </c>
       <c r="B313" s="1">
-        <v>22.7</v>
+        <v>0</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>13</v>
@@ -9423,7 +9423,7 @@
         <v>25</v>
       </c>
       <c r="E313" s="1">
-        <v>0</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
@@ -9431,7 +9431,7 @@
         <v>28</v>
       </c>
       <c r="B314" s="1">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>13</v>
@@ -9440,7 +9440,7 @@
         <v>25</v>
       </c>
       <c r="E314" s="1">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
@@ -9448,7 +9448,7 @@
         <v>28</v>
       </c>
       <c r="B315" s="1">
-        <v>21.8</v>
+        <v>2</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>13</v>
@@ -9457,7 +9457,7 @@
         <v>25</v>
       </c>
       <c r="E315" s="1">
-        <v>2</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
@@ -9465,7 +9465,7 @@
         <v>28</v>
       </c>
       <c r="B316" s="1">
-        <v>21.9</v>
+        <v>3</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>13</v>
@@ -9474,7 +9474,7 @@
         <v>25</v>
       </c>
       <c r="E316" s="1">
-        <v>3</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
@@ -9482,7 +9482,7 @@
         <v>28</v>
       </c>
       <c r="B317" s="1">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>13</v>
@@ -9491,7 +9491,7 @@
         <v>25</v>
       </c>
       <c r="E317" s="1">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
@@ -9499,7 +9499,7 @@
         <v>28</v>
       </c>
       <c r="B318" s="1">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>13</v>
@@ -9508,7 +9508,7 @@
         <v>25</v>
       </c>
       <c r="E318" s="1">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
@@ -9516,7 +9516,7 @@
         <v>28</v>
       </c>
       <c r="B319" s="1">
-        <v>22.6</v>
+        <v>6</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>13</v>
@@ -9525,7 +9525,7 @@
         <v>25</v>
       </c>
       <c r="E319" s="1">
-        <v>6</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
@@ -9533,16 +9533,16 @@
         <v>29</v>
       </c>
       <c r="B320" s="1">
+        <v>0</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E320" s="1">
         <v>24.8</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E320" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
@@ -9550,16 +9550,16 @@
         <v>29</v>
       </c>
       <c r="B321" s="1">
+        <v>1</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E321" s="1">
         <v>26.2</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E321" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
@@ -9567,16 +9567,16 @@
         <v>29</v>
       </c>
       <c r="B322" s="1">
+        <v>2</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E322" s="1">
         <v>30.8</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E322" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
@@ -9584,16 +9584,16 @@
         <v>29</v>
       </c>
       <c r="B323" s="1">
+        <v>3</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E323" s="1">
         <v>31.3</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D323" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E323" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
@@ -9601,16 +9601,16 @@
         <v>29</v>
       </c>
       <c r="B324" s="1">
+        <v>4</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E324" s="1">
         <v>32.5</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E324" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
@@ -9618,16 +9618,16 @@
         <v>29</v>
       </c>
       <c r="B325" s="1">
+        <v>5</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E325" s="1">
         <v>32</v>
-      </c>
-      <c r="C325" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E325" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
@@ -9635,16 +9635,16 @@
         <v>29</v>
       </c>
       <c r="B326" s="1">
+        <v>6</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E326" s="1">
         <v>34.200000000000003</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E326" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
@@ -9652,16 +9652,16 @@
         <v>30</v>
       </c>
       <c r="B327" s="1">
+        <v>0</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E327" s="1">
         <v>23</v>
-      </c>
-      <c r="C327" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D327" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E327" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
@@ -9669,16 +9669,16 @@
         <v>30</v>
       </c>
       <c r="B328" s="1">
+        <v>1</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E328" s="1">
         <v>25.4</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E328" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
@@ -9686,16 +9686,16 @@
         <v>30</v>
       </c>
       <c r="B329" s="1">
+        <v>2</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E329" s="1">
         <v>28.2</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E329" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
@@ -9703,16 +9703,16 @@
         <v>30</v>
       </c>
       <c r="B330" s="1">
+        <v>3</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E330" s="1">
         <v>28.2</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E330" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
@@ -9720,16 +9720,16 @@
         <v>30</v>
       </c>
       <c r="B331" s="1">
+        <v>4</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E331" s="1">
         <v>29.5</v>
-      </c>
-      <c r="C331" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E331" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
@@ -9737,16 +9737,16 @@
         <v>30</v>
       </c>
       <c r="B332" s="1">
+        <v>5</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E332" s="1">
         <v>30.9</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E332" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
@@ -9754,16 +9754,16 @@
         <v>30</v>
       </c>
       <c r="B333" s="1">
+        <v>6</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E333" s="1">
         <v>30.8</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E333" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -9771,16 +9771,16 @@
         <v>31</v>
       </c>
       <c r="B334" s="1">
+        <v>0</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E334" s="1">
         <v>23.4</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E334" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
@@ -9788,16 +9788,16 @@
         <v>31</v>
       </c>
       <c r="B335" s="1">
+        <v>1</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E335" s="1">
         <v>25.2</v>
-      </c>
-      <c r="C335" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E335" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
@@ -9805,16 +9805,16 @@
         <v>31</v>
       </c>
       <c r="B336" s="1">
+        <v>2</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E336" s="1">
         <v>27.4</v>
-      </c>
-      <c r="C336" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E336" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -9822,16 +9822,16 @@
         <v>31</v>
       </c>
       <c r="B337" s="1">
+        <v>3</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E337" s="1">
         <v>28.8</v>
-      </c>
-      <c r="C337" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E337" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
@@ -9839,16 +9839,16 @@
         <v>31</v>
       </c>
       <c r="B338" s="1">
+        <v>4</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E338" s="1">
         <v>28</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E338" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -9856,16 +9856,16 @@
         <v>31</v>
       </c>
       <c r="B339" s="1">
+        <v>5</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E339" s="1">
         <v>28.8</v>
-      </c>
-      <c r="C339" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E339" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
@@ -9873,16 +9873,16 @@
         <v>31</v>
       </c>
       <c r="B340" s="1">
+        <v>6</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E340" s="1">
         <v>29.9</v>
-      </c>
-      <c r="C340" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E340" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
@@ -9890,16 +9890,16 @@
         <v>32</v>
       </c>
       <c r="B341" s="1">
+        <v>0</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E341" s="1">
         <v>26</v>
-      </c>
-      <c r="C341" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E341" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -9907,16 +9907,16 @@
         <v>32</v>
       </c>
       <c r="B342" s="1">
+        <v>1</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E342" s="1">
         <v>28.1</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D342" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E342" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
@@ -9924,16 +9924,16 @@
         <v>32</v>
       </c>
       <c r="B343" s="1">
+        <v>2</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E343" s="1">
         <v>30.6</v>
-      </c>
-      <c r="C343" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E343" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
@@ -9941,16 +9941,16 @@
         <v>32</v>
       </c>
       <c r="B344" s="1">
+        <v>3</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E344" s="1">
         <v>31.7</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E344" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
@@ -9958,16 +9958,16 @@
         <v>32</v>
       </c>
       <c r="B345" s="1">
+        <v>4</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E345" s="1">
         <v>32</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E345" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -9975,16 +9975,16 @@
         <v>32</v>
       </c>
       <c r="B346" s="1">
+        <v>5</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E346" s="1">
         <v>33.700000000000003</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E346" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
@@ -9992,16 +9992,16 @@
         <v>32</v>
       </c>
       <c r="B347" s="1">
+        <v>6</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E347" s="1">
         <v>32.799999999999997</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E347" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -10009,16 +10009,16 @@
         <v>64</v>
       </c>
       <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348" t="s">
+        <v>13</v>
+      </c>
+      <c r="D348" t="s">
+        <v>6</v>
+      </c>
+      <c r="E348">
         <v>24.7</v>
-      </c>
-      <c r="C348" t="s">
-        <v>13</v>
-      </c>
-      <c r="D348" t="s">
-        <v>6</v>
-      </c>
-      <c r="E348">
-        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
@@ -10026,16 +10026,16 @@
         <v>64</v>
       </c>
       <c r="B349">
+        <v>1</v>
+      </c>
+      <c r="C349" t="s">
+        <v>13</v>
+      </c>
+      <c r="D349" t="s">
+        <v>6</v>
+      </c>
+      <c r="E349">
         <v>28.3</v>
-      </c>
-      <c r="C349" t="s">
-        <v>13</v>
-      </c>
-      <c r="D349" t="s">
-        <v>6</v>
-      </c>
-      <c r="E349">
-        <v>1</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
@@ -10043,16 +10043,16 @@
         <v>64</v>
       </c>
       <c r="B350">
+        <v>2</v>
+      </c>
+      <c r="C350" t="s">
+        <v>13</v>
+      </c>
+      <c r="D350" t="s">
+        <v>6</v>
+      </c>
+      <c r="E350">
         <v>29.3</v>
-      </c>
-      <c r="C350" t="s">
-        <v>13</v>
-      </c>
-      <c r="D350" t="s">
-        <v>6</v>
-      </c>
-      <c r="E350">
-        <v>2</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -10060,16 +10060,16 @@
         <v>64</v>
       </c>
       <c r="B351">
+        <v>3</v>
+      </c>
+      <c r="C351" t="s">
+        <v>13</v>
+      </c>
+      <c r="D351" t="s">
+        <v>6</v>
+      </c>
+      <c r="E351">
         <v>31</v>
-      </c>
-      <c r="C351" t="s">
-        <v>13</v>
-      </c>
-      <c r="D351" t="s">
-        <v>6</v>
-      </c>
-      <c r="E351">
-        <v>3</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -10077,16 +10077,16 @@
         <v>64</v>
       </c>
       <c r="B352">
+        <v>4</v>
+      </c>
+      <c r="C352" t="s">
+        <v>13</v>
+      </c>
+      <c r="D352" t="s">
+        <v>6</v>
+      </c>
+      <c r="E352">
         <v>31.3</v>
-      </c>
-      <c r="C352" t="s">
-        <v>13</v>
-      </c>
-      <c r="D352" t="s">
-        <v>6</v>
-      </c>
-      <c r="E352">
-        <v>4</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
@@ -10094,16 +10094,16 @@
         <v>64</v>
       </c>
       <c r="B353">
+        <v>5</v>
+      </c>
+      <c r="C353" t="s">
+        <v>13</v>
+      </c>
+      <c r="D353" t="s">
+        <v>6</v>
+      </c>
+      <c r="E353">
         <v>31.1</v>
-      </c>
-      <c r="C353" t="s">
-        <v>13</v>
-      </c>
-      <c r="D353" t="s">
-        <v>6</v>
-      </c>
-      <c r="E353">
-        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
@@ -10111,16 +10111,16 @@
         <v>64</v>
       </c>
       <c r="B354">
+        <v>6</v>
+      </c>
+      <c r="C354" t="s">
+        <v>13</v>
+      </c>
+      <c r="D354" t="s">
+        <v>6</v>
+      </c>
+      <c r="E354">
         <v>35.5</v>
-      </c>
-      <c r="C354" t="s">
-        <v>13</v>
-      </c>
-      <c r="D354" t="s">
-        <v>6</v>
-      </c>
-      <c r="E354">
-        <v>6</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -10128,16 +10128,16 @@
         <v>65</v>
       </c>
       <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355" t="s">
+        <v>13</v>
+      </c>
+      <c r="D355" t="s">
+        <v>6</v>
+      </c>
+      <c r="E355">
         <v>26.6</v>
-      </c>
-      <c r="C355" t="s">
-        <v>13</v>
-      </c>
-      <c r="D355" t="s">
-        <v>6</v>
-      </c>
-      <c r="E355">
-        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
@@ -10145,16 +10145,16 @@
         <v>65</v>
       </c>
       <c r="B356">
+        <v>1</v>
+      </c>
+      <c r="C356" t="s">
+        <v>13</v>
+      </c>
+      <c r="D356" t="s">
+        <v>6</v>
+      </c>
+      <c r="E356">
         <v>29.4</v>
-      </c>
-      <c r="C356" t="s">
-        <v>13</v>
-      </c>
-      <c r="D356" t="s">
-        <v>6</v>
-      </c>
-      <c r="E356">
-        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
@@ -10162,16 +10162,16 @@
         <v>65</v>
       </c>
       <c r="B357">
+        <v>2</v>
+      </c>
+      <c r="C357" t="s">
+        <v>13</v>
+      </c>
+      <c r="D357" t="s">
+        <v>6</v>
+      </c>
+      <c r="E357">
         <v>29.1</v>
-      </c>
-      <c r="C357" t="s">
-        <v>13</v>
-      </c>
-      <c r="D357" t="s">
-        <v>6</v>
-      </c>
-      <c r="E357">
-        <v>2</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
@@ -10179,16 +10179,16 @@
         <v>65</v>
       </c>
       <c r="B358">
+        <v>3</v>
+      </c>
+      <c r="C358" t="s">
+        <v>13</v>
+      </c>
+      <c r="D358" t="s">
+        <v>6</v>
+      </c>
+      <c r="E358">
         <v>31</v>
-      </c>
-      <c r="C358" t="s">
-        <v>13</v>
-      </c>
-      <c r="D358" t="s">
-        <v>6</v>
-      </c>
-      <c r="E358">
-        <v>3</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -10196,16 +10196,16 @@
         <v>65</v>
       </c>
       <c r="B359">
+        <v>4</v>
+      </c>
+      <c r="C359" t="s">
+        <v>13</v>
+      </c>
+      <c r="D359" t="s">
+        <v>6</v>
+      </c>
+      <c r="E359">
         <v>30.8</v>
-      </c>
-      <c r="C359" t="s">
-        <v>13</v>
-      </c>
-      <c r="D359" t="s">
-        <v>6</v>
-      </c>
-      <c r="E359">
-        <v>4</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -10213,16 +10213,16 @@
         <v>65</v>
       </c>
       <c r="B360">
+        <v>5</v>
+      </c>
+      <c r="C360" t="s">
+        <v>13</v>
+      </c>
+      <c r="D360" t="s">
+        <v>6</v>
+      </c>
+      <c r="E360">
         <v>30.2</v>
-      </c>
-      <c r="C360" t="s">
-        <v>13</v>
-      </c>
-      <c r="D360" t="s">
-        <v>6</v>
-      </c>
-      <c r="E360">
-        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
@@ -10230,16 +10230,16 @@
         <v>65</v>
       </c>
       <c r="B361">
+        <v>6</v>
+      </c>
+      <c r="C361" t="s">
+        <v>13</v>
+      </c>
+      <c r="D361" t="s">
+        <v>6</v>
+      </c>
+      <c r="E361">
         <v>31.3</v>
-      </c>
-      <c r="C361" t="s">
-        <v>13</v>
-      </c>
-      <c r="D361" t="s">
-        <v>6</v>
-      </c>
-      <c r="E361">
-        <v>6</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
@@ -10247,16 +10247,16 @@
         <v>66</v>
       </c>
       <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362" t="s">
+        <v>13</v>
+      </c>
+      <c r="D362" t="s">
+        <v>6</v>
+      </c>
+      <c r="E362">
         <v>26.9</v>
-      </c>
-      <c r="C362" t="s">
-        <v>13</v>
-      </c>
-      <c r="D362" t="s">
-        <v>6</v>
-      </c>
-      <c r="E362">
-        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -10264,16 +10264,16 @@
         <v>66</v>
       </c>
       <c r="B363">
+        <v>1</v>
+      </c>
+      <c r="C363" t="s">
+        <v>13</v>
+      </c>
+      <c r="D363" t="s">
+        <v>6</v>
+      </c>
+      <c r="E363">
         <v>29.3</v>
-      </c>
-      <c r="C363" t="s">
-        <v>13</v>
-      </c>
-      <c r="D363" t="s">
-        <v>6</v>
-      </c>
-      <c r="E363">
-        <v>1</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
@@ -10281,16 +10281,16 @@
         <v>66</v>
       </c>
       <c r="B364">
+        <v>2</v>
+      </c>
+      <c r="C364" t="s">
+        <v>13</v>
+      </c>
+      <c r="D364" t="s">
+        <v>6</v>
+      </c>
+      <c r="E364">
         <v>29.9</v>
-      </c>
-      <c r="C364" t="s">
-        <v>13</v>
-      </c>
-      <c r="D364" t="s">
-        <v>6</v>
-      </c>
-      <c r="E364">
-        <v>2</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
@@ -10298,16 +10298,16 @@
         <v>66</v>
       </c>
       <c r="B365">
+        <v>3</v>
+      </c>
+      <c r="C365" t="s">
+        <v>13</v>
+      </c>
+      <c r="D365" t="s">
+        <v>6</v>
+      </c>
+      <c r="E365">
         <v>30.8</v>
-      </c>
-      <c r="C365" t="s">
-        <v>13</v>
-      </c>
-      <c r="D365" t="s">
-        <v>6</v>
-      </c>
-      <c r="E365">
-        <v>3</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -10315,16 +10315,16 @@
         <v>67</v>
       </c>
       <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366" t="s">
+        <v>13</v>
+      </c>
+      <c r="D366" t="s">
+        <v>6</v>
+      </c>
+      <c r="E366">
         <v>26.9</v>
-      </c>
-      <c r="C366" t="s">
-        <v>13</v>
-      </c>
-      <c r="D366" t="s">
-        <v>6</v>
-      </c>
-      <c r="E366">
-        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
@@ -10332,16 +10332,16 @@
         <v>67</v>
       </c>
       <c r="B367">
+        <v>1</v>
+      </c>
+      <c r="C367" t="s">
+        <v>13</v>
+      </c>
+      <c r="D367" t="s">
+        <v>6</v>
+      </c>
+      <c r="E367">
         <v>29.3</v>
-      </c>
-      <c r="C367" t="s">
-        <v>13</v>
-      </c>
-      <c r="D367" t="s">
-        <v>6</v>
-      </c>
-      <c r="E367">
-        <v>1</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
@@ -10349,16 +10349,16 @@
         <v>67</v>
       </c>
       <c r="B368">
+        <v>2</v>
+      </c>
+      <c r="C368" t="s">
+        <v>13</v>
+      </c>
+      <c r="D368" t="s">
+        <v>6</v>
+      </c>
+      <c r="E368">
         <v>29.9</v>
-      </c>
-      <c r="C368" t="s">
-        <v>13</v>
-      </c>
-      <c r="D368" t="s">
-        <v>6</v>
-      </c>
-      <c r="E368">
-        <v>2</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -10366,16 +10366,16 @@
         <v>67</v>
       </c>
       <c r="B369">
+        <v>3</v>
+      </c>
+      <c r="C369" t="s">
+        <v>13</v>
+      </c>
+      <c r="D369" t="s">
+        <v>6</v>
+      </c>
+      <c r="E369">
         <v>29.9</v>
-      </c>
-      <c r="C369" t="s">
-        <v>13</v>
-      </c>
-      <c r="D369" t="s">
-        <v>6</v>
-      </c>
-      <c r="E369">
-        <v>3</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -10383,16 +10383,16 @@
         <v>67</v>
       </c>
       <c r="B370">
+        <v>4</v>
+      </c>
+      <c r="C370" t="s">
+        <v>13</v>
+      </c>
+      <c r="D370" t="s">
+        <v>6</v>
+      </c>
+      <c r="E370">
         <v>31.9</v>
-      </c>
-      <c r="C370" t="s">
-        <v>13</v>
-      </c>
-      <c r="D370" t="s">
-        <v>6</v>
-      </c>
-      <c r="E370">
-        <v>4</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -10400,16 +10400,16 @@
         <v>67</v>
       </c>
       <c r="B371">
+        <v>5</v>
+      </c>
+      <c r="C371" t="s">
+        <v>13</v>
+      </c>
+      <c r="D371" t="s">
+        <v>6</v>
+      </c>
+      <c r="E371">
         <v>34.299999999999997</v>
-      </c>
-      <c r="C371" t="s">
-        <v>13</v>
-      </c>
-      <c r="D371" t="s">
-        <v>6</v>
-      </c>
-      <c r="E371">
-        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
@@ -10417,16 +10417,16 @@
         <v>67</v>
       </c>
       <c r="B372">
+        <v>6</v>
+      </c>
+      <c r="C372" t="s">
+        <v>13</v>
+      </c>
+      <c r="D372" t="s">
+        <v>6</v>
+      </c>
+      <c r="E372">
         <v>35</v>
-      </c>
-      <c r="C372" t="s">
-        <v>13</v>
-      </c>
-      <c r="D372" t="s">
-        <v>6</v>
-      </c>
-      <c r="E372">
-        <v>6</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
@@ -10434,7 +10434,7 @@
         <v>68</v>
       </c>
       <c r="B373">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C373" t="s">
         <v>13</v>
@@ -10443,7 +10443,7 @@
         <v>25</v>
       </c>
       <c r="E373">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -10451,7 +10451,7 @@
         <v>68</v>
       </c>
       <c r="B374">
-        <v>26.9</v>
+        <v>1</v>
       </c>
       <c r="C374" t="s">
         <v>13</v>
@@ -10460,7 +10460,7 @@
         <v>25</v>
       </c>
       <c r="E374">
-        <v>1</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -10468,7 +10468,7 @@
         <v>68</v>
       </c>
       <c r="B375">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C375" t="s">
         <v>13</v>
@@ -10477,7 +10477,7 @@
         <v>25</v>
       </c>
       <c r="E375">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -10485,7 +10485,7 @@
         <v>68</v>
       </c>
       <c r="B376">
-        <v>26.9</v>
+        <v>3</v>
       </c>
       <c r="C376" t="s">
         <v>13</v>
@@ -10494,7 +10494,7 @@
         <v>25</v>
       </c>
       <c r="E376">
-        <v>3</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
@@ -10502,7 +10502,7 @@
         <v>68</v>
       </c>
       <c r="B377">
-        <v>25.7</v>
+        <v>4</v>
       </c>
       <c r="C377" t="s">
         <v>13</v>
@@ -10511,7 +10511,7 @@
         <v>25</v>
       </c>
       <c r="E377">
-        <v>4</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -10519,7 +10519,7 @@
         <v>68</v>
       </c>
       <c r="B378">
-        <v>25.7</v>
+        <v>5</v>
       </c>
       <c r="C378" t="s">
         <v>13</v>
@@ -10528,7 +10528,7 @@
         <v>25</v>
       </c>
       <c r="E378">
-        <v>5</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
@@ -10536,7 +10536,7 @@
         <v>68</v>
       </c>
       <c r="B379">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C379" t="s">
         <v>13</v>
@@ -10545,7 +10545,7 @@
         <v>25</v>
       </c>
       <c r="E379">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
@@ -10553,7 +10553,7 @@
         <v>69</v>
       </c>
       <c r="B380">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="C380" t="s">
         <v>13</v>
@@ -10562,7 +10562,7 @@
         <v>25</v>
       </c>
       <c r="E380">
-        <v>0</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -10570,7 +10570,7 @@
         <v>69</v>
       </c>
       <c r="B381">
-        <v>28.5</v>
+        <v>1</v>
       </c>
       <c r="C381" t="s">
         <v>13</v>
@@ -10579,7 +10579,7 @@
         <v>25</v>
       </c>
       <c r="E381">
-        <v>1</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -10587,7 +10587,7 @@
         <v>69</v>
       </c>
       <c r="B382">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C382" t="s">
         <v>13</v>
@@ -10596,7 +10596,7 @@
         <v>25</v>
       </c>
       <c r="E382">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
@@ -10604,7 +10604,7 @@
         <v>69</v>
       </c>
       <c r="B383">
-        <v>28.5</v>
+        <v>3</v>
       </c>
       <c r="C383" t="s">
         <v>13</v>
@@ -10613,7 +10613,7 @@
         <v>25</v>
       </c>
       <c r="E383">
-        <v>3</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
@@ -10621,7 +10621,7 @@
         <v>69</v>
       </c>
       <c r="B384">
-        <v>28.5</v>
+        <v>4</v>
       </c>
       <c r="C384" t="s">
         <v>13</v>
@@ -10630,7 +10630,7 @@
         <v>25</v>
       </c>
       <c r="E384">
-        <v>4</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
@@ -10638,7 +10638,7 @@
         <v>69</v>
       </c>
       <c r="B385">
-        <v>28.5</v>
+        <v>5</v>
       </c>
       <c r="C385" t="s">
         <v>13</v>
@@ -10647,7 +10647,7 @@
         <v>25</v>
       </c>
       <c r="E385">
-        <v>5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
@@ -10655,7 +10655,7 @@
         <v>69</v>
       </c>
       <c r="B386">
-        <v>29.1</v>
+        <v>6</v>
       </c>
       <c r="C386" t="s">
         <v>13</v>
@@ -10664,7 +10664,7 @@
         <v>25</v>
       </c>
       <c r="E386">
-        <v>6</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
@@ -10672,7 +10672,7 @@
         <v>70</v>
       </c>
       <c r="B387">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="C387" t="s">
         <v>13</v>
@@ -10681,7 +10681,7 @@
         <v>25</v>
       </c>
       <c r="E387">
-        <v>0</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
@@ -10689,7 +10689,7 @@
         <v>70</v>
       </c>
       <c r="B388">
-        <v>27.3</v>
+        <v>1</v>
       </c>
       <c r="C388" t="s">
         <v>13</v>
@@ -10698,7 +10698,7 @@
         <v>25</v>
       </c>
       <c r="E388">
-        <v>1</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -10706,7 +10706,7 @@
         <v>70</v>
       </c>
       <c r="B389">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C389" t="s">
         <v>13</v>
@@ -10715,7 +10715,7 @@
         <v>25</v>
       </c>
       <c r="E389">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
@@ -10723,7 +10723,7 @@
         <v>70</v>
       </c>
       <c r="B390">
-        <v>27.3</v>
+        <v>3</v>
       </c>
       <c r="C390" t="s">
         <v>13</v>
@@ -10732,7 +10732,7 @@
         <v>25</v>
       </c>
       <c r="E390">
-        <v>3</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
@@ -10740,7 +10740,7 @@
         <v>70</v>
       </c>
       <c r="B391">
-        <v>29.3</v>
+        <v>4</v>
       </c>
       <c r="C391" t="s">
         <v>13</v>
@@ -10749,7 +10749,7 @@
         <v>25</v>
       </c>
       <c r="E391">
-        <v>4</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
@@ -10757,7 +10757,7 @@
         <v>70</v>
       </c>
       <c r="B392">
-        <v>29.3</v>
+        <v>5</v>
       </c>
       <c r="C392" t="s">
         <v>13</v>
@@ -10766,7 +10766,7 @@
         <v>25</v>
       </c>
       <c r="E392">
-        <v>5</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -10774,7 +10774,7 @@
         <v>70</v>
       </c>
       <c r="B393">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C393" t="s">
         <v>13</v>
@@ -10783,7 +10783,7 @@
         <v>25</v>
       </c>
       <c r="E393">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
@@ -10791,16 +10791,16 @@
         <v>71</v>
       </c>
       <c r="B394">
+        <v>0</v>
+      </c>
+      <c r="C394" t="s">
+        <v>13</v>
+      </c>
+      <c r="D394" t="s">
+        <v>6</v>
+      </c>
+      <c r="E394">
         <v>22.5</v>
-      </c>
-      <c r="C394" t="s">
-        <v>13</v>
-      </c>
-      <c r="D394" t="s">
-        <v>6</v>
-      </c>
-      <c r="E394">
-        <v>0</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
@@ -10808,16 +10808,16 @@
         <v>71</v>
       </c>
       <c r="B395">
+        <v>1</v>
+      </c>
+      <c r="C395" t="s">
+        <v>13</v>
+      </c>
+      <c r="D395" t="s">
+        <v>6</v>
+      </c>
+      <c r="E395">
         <v>32.9</v>
-      </c>
-      <c r="C395" t="s">
-        <v>13</v>
-      </c>
-      <c r="D395" t="s">
-        <v>6</v>
-      </c>
-      <c r="E395">
-        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
@@ -10825,16 +10825,16 @@
         <v>71</v>
       </c>
       <c r="B396">
+        <v>2</v>
+      </c>
+      <c r="C396" t="s">
+        <v>13</v>
+      </c>
+      <c r="D396" t="s">
+        <v>6</v>
+      </c>
+      <c r="E396">
         <v>28</v>
-      </c>
-      <c r="C396" t="s">
-        <v>13</v>
-      </c>
-      <c r="D396" t="s">
-        <v>6</v>
-      </c>
-      <c r="E396">
-        <v>2</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
@@ -10842,16 +10842,16 @@
         <v>71</v>
       </c>
       <c r="B397">
+        <v>3</v>
+      </c>
+      <c r="C397" t="s">
+        <v>13</v>
+      </c>
+      <c r="D397" t="s">
+        <v>6</v>
+      </c>
+      <c r="E397">
         <v>32.200000000000003</v>
-      </c>
-      <c r="C397" t="s">
-        <v>13</v>
-      </c>
-      <c r="D397" t="s">
-        <v>6</v>
-      </c>
-      <c r="E397">
-        <v>3</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
@@ -10859,16 +10859,16 @@
         <v>71</v>
       </c>
       <c r="B398">
+        <v>4</v>
+      </c>
+      <c r="C398" t="s">
+        <v>13</v>
+      </c>
+      <c r="D398" t="s">
+        <v>6</v>
+      </c>
+      <c r="E398">
         <v>31.1</v>
-      </c>
-      <c r="C398" t="s">
-        <v>13</v>
-      </c>
-      <c r="D398" t="s">
-        <v>6</v>
-      </c>
-      <c r="E398">
-        <v>4</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
@@ -10876,16 +10876,16 @@
         <v>71</v>
       </c>
       <c r="B399">
+        <v>5</v>
+      </c>
+      <c r="C399" t="s">
+        <v>13</v>
+      </c>
+      <c r="D399" t="s">
+        <v>6</v>
+      </c>
+      <c r="E399">
         <v>35</v>
-      </c>
-      <c r="C399" t="s">
-        <v>13</v>
-      </c>
-      <c r="D399" t="s">
-        <v>6</v>
-      </c>
-      <c r="E399">
-        <v>5</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
@@ -10893,16 +10893,16 @@
         <v>71</v>
       </c>
       <c r="B400">
+        <v>5</v>
+      </c>
+      <c r="C400" t="s">
+        <v>13</v>
+      </c>
+      <c r="D400" t="s">
+        <v>6</v>
+      </c>
+      <c r="E400">
         <v>35</v>
-      </c>
-      <c r="C400" t="s">
-        <v>13</v>
-      </c>
-      <c r="D400" t="s">
-        <v>6</v>
-      </c>
-      <c r="E400">
-        <v>5</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
@@ -10910,16 +10910,16 @@
         <v>71</v>
       </c>
       <c r="B401">
+        <v>6</v>
+      </c>
+      <c r="C401" t="s">
+        <v>13</v>
+      </c>
+      <c r="D401" t="s">
+        <v>6</v>
+      </c>
+      <c r="E401">
         <v>38.200000000000003</v>
-      </c>
-      <c r="C401" t="s">
-        <v>13</v>
-      </c>
-      <c r="D401" t="s">
-        <v>6</v>
-      </c>
-      <c r="E401">
-        <v>6</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
@@ -10927,16 +10927,16 @@
         <v>72</v>
       </c>
       <c r="B402">
+        <v>0</v>
+      </c>
+      <c r="C402" t="s">
+        <v>13</v>
+      </c>
+      <c r="D402" t="s">
+        <v>6</v>
+      </c>
+      <c r="E402">
         <v>26.4</v>
-      </c>
-      <c r="C402" t="s">
-        <v>13</v>
-      </c>
-      <c r="D402" t="s">
-        <v>6</v>
-      </c>
-      <c r="E402">
-        <v>0</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
@@ -10944,16 +10944,16 @@
         <v>72</v>
       </c>
       <c r="B403">
+        <v>1</v>
+      </c>
+      <c r="C403" t="s">
+        <v>13</v>
+      </c>
+      <c r="D403" t="s">
+        <v>6</v>
+      </c>
+      <c r="E403">
         <v>31</v>
-      </c>
-      <c r="C403" t="s">
-        <v>13</v>
-      </c>
-      <c r="D403" t="s">
-        <v>6</v>
-      </c>
-      <c r="E403">
-        <v>1</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
@@ -10961,16 +10961,16 @@
         <v>72</v>
       </c>
       <c r="B404">
+        <v>2</v>
+      </c>
+      <c r="C404" t="s">
+        <v>13</v>
+      </c>
+      <c r="D404" t="s">
+        <v>6</v>
+      </c>
+      <c r="E404">
         <v>36.700000000000003</v>
-      </c>
-      <c r="C404" t="s">
-        <v>13</v>
-      </c>
-      <c r="D404" t="s">
-        <v>6</v>
-      </c>
-      <c r="E404">
-        <v>2</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
@@ -10978,16 +10978,16 @@
         <v>72</v>
       </c>
       <c r="B405">
+        <v>3</v>
+      </c>
+      <c r="C405" t="s">
+        <v>13</v>
+      </c>
+      <c r="D405" t="s">
+        <v>6</v>
+      </c>
+      <c r="E405">
         <v>38</v>
-      </c>
-      <c r="C405" t="s">
-        <v>13</v>
-      </c>
-      <c r="D405" t="s">
-        <v>6</v>
-      </c>
-      <c r="E405">
-        <v>3</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
@@ -10995,16 +10995,16 @@
         <v>72</v>
       </c>
       <c r="B406">
+        <v>4</v>
+      </c>
+      <c r="C406" t="s">
+        <v>13</v>
+      </c>
+      <c r="D406" t="s">
+        <v>6</v>
+      </c>
+      <c r="E406">
         <v>38.799999999999997</v>
-      </c>
-      <c r="C406" t="s">
-        <v>13</v>
-      </c>
-      <c r="D406" t="s">
-        <v>6</v>
-      </c>
-      <c r="E406">
-        <v>4</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
@@ -11012,16 +11012,16 @@
         <v>72</v>
       </c>
       <c r="B407">
+        <v>5</v>
+      </c>
+      <c r="C407" t="s">
+        <v>13</v>
+      </c>
+      <c r="D407" t="s">
+        <v>6</v>
+      </c>
+      <c r="E407">
         <v>42.5</v>
-      </c>
-      <c r="C407" t="s">
-        <v>13</v>
-      </c>
-      <c r="D407" t="s">
-        <v>6</v>
-      </c>
-      <c r="E407">
-        <v>5</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
@@ -11029,16 +11029,16 @@
         <v>72</v>
       </c>
       <c r="B408">
+        <v>5</v>
+      </c>
+      <c r="C408" t="s">
+        <v>13</v>
+      </c>
+      <c r="D408" t="s">
+        <v>6</v>
+      </c>
+      <c r="E408">
         <v>42.5</v>
-      </c>
-      <c r="C408" t="s">
-        <v>13</v>
-      </c>
-      <c r="D408" t="s">
-        <v>6</v>
-      </c>
-      <c r="E408">
-        <v>5</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
@@ -11046,16 +11046,16 @@
         <v>72</v>
       </c>
       <c r="B409">
+        <v>6</v>
+      </c>
+      <c r="C409" t="s">
+        <v>13</v>
+      </c>
+      <c r="D409" t="s">
+        <v>6</v>
+      </c>
+      <c r="E409">
         <v>44.3</v>
-      </c>
-      <c r="C409" t="s">
-        <v>13</v>
-      </c>
-      <c r="D409" t="s">
-        <v>6</v>
-      </c>
-      <c r="E409">
-        <v>6</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
@@ -11063,16 +11063,16 @@
         <v>73</v>
       </c>
       <c r="B410">
+        <v>0</v>
+      </c>
+      <c r="C410" t="s">
+        <v>13</v>
+      </c>
+      <c r="D410" t="s">
+        <v>6</v>
+      </c>
+      <c r="E410">
         <v>24.2</v>
-      </c>
-      <c r="C410" t="s">
-        <v>13</v>
-      </c>
-      <c r="D410" t="s">
-        <v>6</v>
-      </c>
-      <c r="E410">
-        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
@@ -11080,16 +11080,16 @@
         <v>73</v>
       </c>
       <c r="B411">
+        <v>1</v>
+      </c>
+      <c r="C411" t="s">
+        <v>13</v>
+      </c>
+      <c r="D411" t="s">
+        <v>6</v>
+      </c>
+      <c r="E411">
         <v>34</v>
-      </c>
-      <c r="C411" t="s">
-        <v>13</v>
-      </c>
-      <c r="D411" t="s">
-        <v>6</v>
-      </c>
-      <c r="E411">
-        <v>1</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
@@ -11097,16 +11097,16 @@
         <v>73</v>
       </c>
       <c r="B412">
+        <v>2</v>
+      </c>
+      <c r="C412" t="s">
+        <v>13</v>
+      </c>
+      <c r="D412" t="s">
+        <v>6</v>
+      </c>
+      <c r="E412">
         <v>30.4</v>
-      </c>
-      <c r="C412" t="s">
-        <v>13</v>
-      </c>
-      <c r="D412" t="s">
-        <v>6</v>
-      </c>
-      <c r="E412">
-        <v>2</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
@@ -11114,16 +11114,16 @@
         <v>73</v>
       </c>
       <c r="B413">
+        <v>3</v>
+      </c>
+      <c r="C413" t="s">
+        <v>13</v>
+      </c>
+      <c r="D413" t="s">
+        <v>6</v>
+      </c>
+      <c r="E413">
         <v>30</v>
-      </c>
-      <c r="C413" t="s">
-        <v>13</v>
-      </c>
-      <c r="D413" t="s">
-        <v>6</v>
-      </c>
-      <c r="E413">
-        <v>3</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -11131,16 +11131,16 @@
         <v>73</v>
       </c>
       <c r="B414">
+        <v>4</v>
+      </c>
+      <c r="C414" t="s">
+        <v>13</v>
+      </c>
+      <c r="D414" t="s">
+        <v>6</v>
+      </c>
+      <c r="E414">
         <v>32.200000000000003</v>
-      </c>
-      <c r="C414" t="s">
-        <v>13</v>
-      </c>
-      <c r="D414" t="s">
-        <v>6</v>
-      </c>
-      <c r="E414">
-        <v>4</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
@@ -11148,16 +11148,16 @@
         <v>73</v>
       </c>
       <c r="B415">
+        <v>5</v>
+      </c>
+      <c r="C415" t="s">
+        <v>13</v>
+      </c>
+      <c r="D415" t="s">
+        <v>6</v>
+      </c>
+      <c r="E415">
         <v>31.8</v>
-      </c>
-      <c r="C415" t="s">
-        <v>13</v>
-      </c>
-      <c r="D415" t="s">
-        <v>6</v>
-      </c>
-      <c r="E415">
-        <v>5</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
@@ -11165,16 +11165,16 @@
         <v>73</v>
       </c>
       <c r="B416">
+        <v>5</v>
+      </c>
+      <c r="C416" t="s">
+        <v>13</v>
+      </c>
+      <c r="D416" t="s">
+        <v>6</v>
+      </c>
+      <c r="E416">
         <v>31.8</v>
-      </c>
-      <c r="C416" t="s">
-        <v>13</v>
-      </c>
-      <c r="D416" t="s">
-        <v>6</v>
-      </c>
-      <c r="E416">
-        <v>5</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -11182,16 +11182,16 @@
         <v>73</v>
       </c>
       <c r="B417">
+        <v>6</v>
+      </c>
+      <c r="C417" t="s">
+        <v>13</v>
+      </c>
+      <c r="D417" t="s">
+        <v>6</v>
+      </c>
+      <c r="E417">
         <v>33</v>
-      </c>
-      <c r="C417" t="s">
-        <v>13</v>
-      </c>
-      <c r="D417" t="s">
-        <v>6</v>
-      </c>
-      <c r="E417">
-        <v>6</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
@@ -11199,16 +11199,16 @@
         <v>74</v>
       </c>
       <c r="B418">
+        <v>0</v>
+      </c>
+      <c r="C418" t="s">
+        <v>13</v>
+      </c>
+      <c r="D418" t="s">
+        <v>6</v>
+      </c>
+      <c r="E418">
         <v>26.3</v>
-      </c>
-      <c r="C418" t="s">
-        <v>13</v>
-      </c>
-      <c r="D418" t="s">
-        <v>6</v>
-      </c>
-      <c r="E418">
-        <v>0</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -11216,16 +11216,16 @@
         <v>74</v>
       </c>
       <c r="B419">
+        <v>1</v>
+      </c>
+      <c r="C419" t="s">
+        <v>13</v>
+      </c>
+      <c r="D419" t="s">
+        <v>6</v>
+      </c>
+      <c r="E419">
         <v>31.5</v>
-      </c>
-      <c r="C419" t="s">
-        <v>13</v>
-      </c>
-      <c r="D419" t="s">
-        <v>6</v>
-      </c>
-      <c r="E419">
-        <v>1</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -11233,16 +11233,16 @@
         <v>74</v>
       </c>
       <c r="B420">
+        <v>2</v>
+      </c>
+      <c r="C420" t="s">
+        <v>13</v>
+      </c>
+      <c r="D420" t="s">
+        <v>6</v>
+      </c>
+      <c r="E420">
         <v>29.8</v>
-      </c>
-      <c r="C420" t="s">
-        <v>13</v>
-      </c>
-      <c r="D420" t="s">
-        <v>6</v>
-      </c>
-      <c r="E420">
-        <v>2</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
@@ -11250,16 +11250,16 @@
         <v>74</v>
       </c>
       <c r="B421">
+        <v>3</v>
+      </c>
+      <c r="C421" t="s">
+        <v>13</v>
+      </c>
+      <c r="D421" t="s">
+        <v>6</v>
+      </c>
+      <c r="E421">
         <v>30.1</v>
-      </c>
-      <c r="C421" t="s">
-        <v>13</v>
-      </c>
-      <c r="D421" t="s">
-        <v>6</v>
-      </c>
-      <c r="E421">
-        <v>3</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
@@ -11267,16 +11267,16 @@
         <v>74</v>
       </c>
       <c r="B422">
+        <v>4</v>
+      </c>
+      <c r="C422" t="s">
+        <v>13</v>
+      </c>
+      <c r="D422" t="s">
+        <v>6</v>
+      </c>
+      <c r="E422">
         <v>31</v>
-      </c>
-      <c r="C422" t="s">
-        <v>13</v>
-      </c>
-      <c r="D422" t="s">
-        <v>6</v>
-      </c>
-      <c r="E422">
-        <v>4</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
@@ -11284,16 +11284,16 @@
         <v>74</v>
       </c>
       <c r="B423">
+        <v>5</v>
+      </c>
+      <c r="C423" t="s">
+        <v>13</v>
+      </c>
+      <c r="D423" t="s">
+        <v>6</v>
+      </c>
+      <c r="E423">
         <v>32.9</v>
-      </c>
-      <c r="C423" t="s">
-        <v>13</v>
-      </c>
-      <c r="D423" t="s">
-        <v>6</v>
-      </c>
-      <c r="E423">
-        <v>5</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
@@ -11301,16 +11301,16 @@
         <v>74</v>
       </c>
       <c r="B424">
+        <v>5</v>
+      </c>
+      <c r="C424" t="s">
+        <v>13</v>
+      </c>
+      <c r="D424" t="s">
+        <v>6</v>
+      </c>
+      <c r="E424">
         <v>32.9</v>
-      </c>
-      <c r="C424" t="s">
-        <v>13</v>
-      </c>
-      <c r="D424" t="s">
-        <v>6</v>
-      </c>
-      <c r="E424">
-        <v>5</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
@@ -11318,16 +11318,16 @@
         <v>74</v>
       </c>
       <c r="B425">
+        <v>6</v>
+      </c>
+      <c r="C425" t="s">
+        <v>13</v>
+      </c>
+      <c r="D425" t="s">
+        <v>6</v>
+      </c>
+      <c r="E425">
         <v>35</v>
-      </c>
-      <c r="C425" t="s">
-        <v>13</v>
-      </c>
-      <c r="D425" t="s">
-        <v>6</v>
-      </c>
-      <c r="E425">
-        <v>6</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
@@ -11335,7 +11335,7 @@
         <v>75</v>
       </c>
       <c r="B426">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="C426" t="s">
         <v>13</v>
@@ -11344,7 +11344,7 @@
         <v>25</v>
       </c>
       <c r="E426">
-        <v>0</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
@@ -11352,7 +11352,7 @@
         <v>75</v>
       </c>
       <c r="B427">
-        <v>21.4</v>
+        <v>1</v>
       </c>
       <c r="C427" t="s">
         <v>13</v>
@@ -11361,7 +11361,7 @@
         <v>25</v>
       </c>
       <c r="E427">
-        <v>1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
@@ -11369,7 +11369,7 @@
         <v>75</v>
       </c>
       <c r="B428">
-        <v>26.3</v>
+        <v>2</v>
       </c>
       <c r="C428" t="s">
         <v>13</v>
@@ -11378,7 +11378,7 @@
         <v>25</v>
       </c>
       <c r="E428">
-        <v>2</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
@@ -11386,7 +11386,7 @@
         <v>75</v>
       </c>
       <c r="B429">
-        <v>28.5</v>
+        <v>3</v>
       </c>
       <c r="C429" t="s">
         <v>13</v>
@@ -11395,7 +11395,7 @@
         <v>25</v>
       </c>
       <c r="E429">
-        <v>3</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
@@ -11403,7 +11403,7 @@
         <v>75</v>
       </c>
       <c r="B430">
-        <v>28.6</v>
+        <v>4</v>
       </c>
       <c r="C430" t="s">
         <v>13</v>
@@ -11412,7 +11412,7 @@
         <v>25</v>
       </c>
       <c r="E430">
-        <v>4</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
@@ -11420,7 +11420,7 @@
         <v>75</v>
       </c>
       <c r="B431">
-        <v>25.5</v>
+        <v>5</v>
       </c>
       <c r="C431" t="s">
         <v>13</v>
@@ -11429,7 +11429,7 @@
         <v>25</v>
       </c>
       <c r="E431">
-        <v>5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
@@ -11437,7 +11437,7 @@
         <v>75</v>
       </c>
       <c r="B432">
-        <v>25.7</v>
+        <v>6</v>
       </c>
       <c r="C432" t="s">
         <v>13</v>
@@ -11446,7 +11446,7 @@
         <v>25</v>
       </c>
       <c r="E432">
-        <v>6</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
@@ -11454,7 +11454,7 @@
         <v>76</v>
       </c>
       <c r="B433">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C433" t="s">
         <v>13</v>
@@ -11463,7 +11463,7 @@
         <v>25</v>
       </c>
       <c r="E433">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
@@ -11471,7 +11471,7 @@
         <v>76</v>
       </c>
       <c r="B434">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C434" t="s">
         <v>13</v>
@@ -11480,7 +11480,7 @@
         <v>25</v>
       </c>
       <c r="E434">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
@@ -11488,7 +11488,7 @@
         <v>76</v>
       </c>
       <c r="B435">
-        <v>27.6</v>
+        <v>2</v>
       </c>
       <c r="C435" t="s">
         <v>13</v>
@@ -11497,7 +11497,7 @@
         <v>25</v>
       </c>
       <c r="E435">
-        <v>2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
@@ -11505,7 +11505,7 @@
         <v>76</v>
       </c>
       <c r="B436">
-        <v>27.8</v>
+        <v>3</v>
       </c>
       <c r="C436" t="s">
         <v>13</v>
@@ -11514,7 +11514,7 @@
         <v>25</v>
       </c>
       <c r="E436">
-        <v>3</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
@@ -11522,7 +11522,7 @@
         <v>76</v>
       </c>
       <c r="B437">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C437" t="s">
         <v>13</v>
@@ -11531,7 +11531,7 @@
         <v>25</v>
       </c>
       <c r="E437">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
@@ -11539,7 +11539,7 @@
         <v>76</v>
       </c>
       <c r="B438">
-        <v>28.3</v>
+        <v>5</v>
       </c>
       <c r="C438" t="s">
         <v>13</v>
@@ -11548,7 +11548,7 @@
         <v>25</v>
       </c>
       <c r="E438">
-        <v>5</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
@@ -11556,7 +11556,7 @@
         <v>76</v>
       </c>
       <c r="B439">
-        <v>28.3</v>
+        <v>6</v>
       </c>
       <c r="C439" t="s">
         <v>13</v>
@@ -11565,7 +11565,7 @@
         <v>25</v>
       </c>
       <c r="E439">
-        <v>6</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
@@ -11573,7 +11573,7 @@
         <v>77</v>
       </c>
       <c r="B440">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="C440" t="s">
         <v>13</v>
@@ -11582,7 +11582,7 @@
         <v>25</v>
       </c>
       <c r="E440">
-        <v>0</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
@@ -11590,7 +11590,7 @@
         <v>77</v>
       </c>
       <c r="B441">
-        <v>26.5</v>
+        <v>1</v>
       </c>
       <c r="C441" t="s">
         <v>13</v>
@@ -11599,7 +11599,7 @@
         <v>25</v>
       </c>
       <c r="E441">
-        <v>1</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
@@ -11607,7 +11607,7 @@
         <v>77</v>
       </c>
       <c r="B442">
-        <v>26.5</v>
+        <v>2</v>
       </c>
       <c r="C442" t="s">
         <v>13</v>
@@ -11616,7 +11616,7 @@
         <v>25</v>
       </c>
       <c r="E442">
-        <v>2</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
@@ -11624,7 +11624,7 @@
         <v>77</v>
       </c>
       <c r="B443">
-        <v>27.2</v>
+        <v>3</v>
       </c>
       <c r="C443" t="s">
         <v>13</v>
@@ -11633,7 +11633,7 @@
         <v>25</v>
       </c>
       <c r="E443">
-        <v>3</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
@@ -11641,7 +11641,7 @@
         <v>77</v>
       </c>
       <c r="B444">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C444" t="s">
         <v>13</v>
@@ -11650,7 +11650,7 @@
         <v>25</v>
       </c>
       <c r="E444">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
@@ -11658,7 +11658,7 @@
         <v>77</v>
       </c>
       <c r="B445">
-        <v>27.7</v>
+        <v>5</v>
       </c>
       <c r="C445" t="s">
         <v>13</v>
@@ -11667,7 +11667,7 @@
         <v>25</v>
       </c>
       <c r="E445">
-        <v>5</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
@@ -11675,7 +11675,7 @@
         <v>77</v>
       </c>
       <c r="B446">
-        <v>26.5</v>
+        <v>6</v>
       </c>
       <c r="C446" t="s">
         <v>13</v>
@@ -11684,7 +11684,7 @@
         <v>25</v>
       </c>
       <c r="E446">
-        <v>6</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
@@ -11692,7 +11692,7 @@
         <v>78</v>
       </c>
       <c r="B447">
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="C447" t="s">
         <v>13</v>
@@ -11701,7 +11701,7 @@
         <v>25</v>
       </c>
       <c r="E447">
-        <v>0</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
@@ -11709,7 +11709,7 @@
         <v>78</v>
       </c>
       <c r="B448">
-        <v>26.3</v>
+        <v>1</v>
       </c>
       <c r="C448" t="s">
         <v>13</v>
@@ -11718,7 +11718,7 @@
         <v>25</v>
       </c>
       <c r="E448">
-        <v>1</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -11726,7 +11726,7 @@
         <v>78</v>
       </c>
       <c r="B449">
-        <v>26.3</v>
+        <v>2</v>
       </c>
       <c r="C449" t="s">
         <v>13</v>
@@ -11735,7 +11735,7 @@
         <v>25</v>
       </c>
       <c r="E449">
-        <v>2</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
@@ -11743,7 +11743,7 @@
         <v>78</v>
       </c>
       <c r="B450">
-        <v>25.5</v>
+        <v>3</v>
       </c>
       <c r="C450" t="s">
         <v>13</v>
@@ -11752,7 +11752,7 @@
         <v>25</v>
       </c>
       <c r="E450">
-        <v>3</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -11760,7 +11760,7 @@
         <v>78</v>
       </c>
       <c r="B451">
-        <v>25.8</v>
+        <v>4</v>
       </c>
       <c r="C451" t="s">
         <v>13</v>
@@ -11769,7 +11769,7 @@
         <v>25</v>
       </c>
       <c r="E451">
-        <v>4</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
@@ -11777,7 +11777,7 @@
         <v>78</v>
       </c>
       <c r="B452">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C452" t="s">
         <v>13</v>
@@ -11786,7 +11786,7 @@
         <v>25</v>
       </c>
       <c r="E452">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
@@ -11794,7 +11794,7 @@
         <v>78</v>
       </c>
       <c r="B453">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C453" t="s">
         <v>13</v>
@@ -11803,7 +11803,7 @@
         <v>25</v>
       </c>
       <c r="E453">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Figure2/Weight/Weight.xlsx
+++ b/Data/Figure2/Weight/Weight.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure2\Weight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE39B7C-3B1A-4199-91CF-A0C8FCBAE4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52E8FEFD-18E3-46F7-91FA-40093F6F785A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9056,14 +9056,14 @@
       <c r="A292" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B292" s="1">
-        <v>0</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>13</v>
+      <c r="B292" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C292" s="1">
+        <v>0</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E292" s="1">
         <v>21.2</v>
@@ -9073,14 +9073,14 @@
       <c r="A293" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B293" s="1">
+      <c r="B293" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C293" s="1">
         <v>1</v>
       </c>
-      <c r="C293" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D293" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E293" s="1">
         <v>21.4</v>
@@ -9090,14 +9090,14 @@
       <c r="A294" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B294" s="1">
+      <c r="B294" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C294" s="1">
         <v>2</v>
       </c>
-      <c r="C294" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D294" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E294" s="1">
         <v>21.7</v>
@@ -9107,14 +9107,14 @@
       <c r="A295" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B295" s="1">
+      <c r="B295" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C295" s="1">
         <v>3</v>
       </c>
-      <c r="C295" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D295" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E295" s="1">
         <v>21.8</v>
@@ -9124,14 +9124,14 @@
       <c r="A296" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B296" s="1">
+      <c r="B296" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C296" s="1">
         <v>4</v>
       </c>
-      <c r="C296" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D296" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E296" s="1">
         <v>22.8</v>
@@ -9141,14 +9141,14 @@
       <c r="A297" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B297" s="1">
+      <c r="B297" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C297" s="1">
         <v>5</v>
       </c>
-      <c r="C297" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D297" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E297" s="1">
         <v>22.8</v>
@@ -9158,14 +9158,14 @@
       <c r="A298" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B298" s="1">
-        <v>6</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>13</v>
+      <c r="B298" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C298" s="1">
+        <v>6</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E298" s="1">
         <v>23</v>
@@ -9175,14 +9175,14 @@
       <c r="A299" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B299" s="1">
-        <v>0</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>13</v>
+      <c r="B299" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C299" s="1">
+        <v>0</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E299" s="1">
         <v>24</v>
@@ -9192,14 +9192,14 @@
       <c r="A300" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B300" s="1">
+      <c r="B300" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C300" s="1">
         <v>1</v>
       </c>
-      <c r="C300" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D300" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E300" s="1">
         <v>24.5</v>
@@ -9209,14 +9209,14 @@
       <c r="A301" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B301" s="1">
+      <c r="B301" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C301" s="1">
         <v>2</v>
       </c>
-      <c r="C301" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D301" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E301" s="1">
         <v>24.4</v>
@@ -9226,14 +9226,14 @@
       <c r="A302" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B302" s="1">
+      <c r="B302" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C302" s="1">
         <v>3</v>
       </c>
-      <c r="C302" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D302" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E302" s="1">
         <v>24.3</v>
@@ -9243,14 +9243,14 @@
       <c r="A303" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B303" s="1">
+      <c r="B303" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C303" s="1">
         <v>4</v>
       </c>
-      <c r="C303" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D303" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E303" s="1">
         <v>27</v>
@@ -9260,14 +9260,14 @@
       <c r="A304" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B304" s="1">
+      <c r="B304" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C304" s="1">
         <v>5</v>
       </c>
-      <c r="C304" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D304" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E304" s="1">
         <v>27</v>
@@ -9277,14 +9277,14 @@
       <c r="A305" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B305" s="1">
-        <v>6</v>
-      </c>
-      <c r="C305" s="1" t="s">
-        <v>13</v>
+      <c r="B305" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C305" s="1">
+        <v>6</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E305" s="1">
         <v>26</v>
@@ -9294,14 +9294,14 @@
       <c r="A306" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B306" s="1">
-        <v>0</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>13</v>
+      <c r="B306" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C306" s="1">
+        <v>0</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E306" s="1">
         <v>24.9</v>
@@ -9311,14 +9311,14 @@
       <c r="A307" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B307" s="1">
+      <c r="B307" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C307" s="1">
         <v>1</v>
       </c>
-      <c r="C307" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D307" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E307" s="1">
         <v>25.2</v>
@@ -9328,14 +9328,14 @@
       <c r="A308" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B308" s="1">
+      <c r="B308" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C308" s="1">
         <v>2</v>
       </c>
-      <c r="C308" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D308" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E308" s="1">
         <v>25.9</v>
@@ -9345,14 +9345,14 @@
       <c r="A309" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B309" s="1">
+      <c r="B309" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C309" s="1">
         <v>3</v>
       </c>
-      <c r="C309" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D309" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E309" s="1">
         <v>25.8</v>
@@ -9362,14 +9362,14 @@
       <c r="A310" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B310" s="1">
+      <c r="B310" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C310" s="1">
         <v>4</v>
       </c>
-      <c r="C310" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D310" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E310" s="1">
         <v>26.2</v>
@@ -9379,14 +9379,14 @@
       <c r="A311" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B311" s="1">
+      <c r="B311" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C311" s="1">
         <v>5</v>
       </c>
-      <c r="C311" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D311" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E311" s="1">
         <v>26.2</v>
@@ -9396,14 +9396,14 @@
       <c r="A312" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B312" s="1">
-        <v>6</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>13</v>
+      <c r="B312" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C312" s="1">
+        <v>6</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E312" s="1">
         <v>26.2</v>
@@ -9413,14 +9413,14 @@
       <c r="A313" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B313" s="1">
-        <v>0</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>13</v>
+      <c r="B313" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C313" s="1">
+        <v>0</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E313" s="1">
         <v>22.7</v>
@@ -9430,14 +9430,14 @@
       <c r="A314" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B314" s="1">
+      <c r="B314" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C314" s="1">
         <v>1</v>
       </c>
-      <c r="C314" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D314" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E314" s="1">
         <v>22</v>
@@ -9447,14 +9447,14 @@
       <c r="A315" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B315" s="1">
+      <c r="B315" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C315" s="1">
         <v>2</v>
       </c>
-      <c r="C315" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D315" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E315" s="1">
         <v>21.8</v>
@@ -9464,14 +9464,14 @@
       <c r="A316" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B316" s="1">
+      <c r="B316" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C316" s="1">
         <v>3</v>
       </c>
-      <c r="C316" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D316" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E316" s="1">
         <v>21.9</v>
@@ -9481,14 +9481,14 @@
       <c r="A317" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B317" s="1">
+      <c r="B317" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C317" s="1">
         <v>4</v>
       </c>
-      <c r="C317" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D317" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E317" s="1">
         <v>22</v>
@@ -9498,14 +9498,14 @@
       <c r="A318" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B318" s="1">
+      <c r="B318" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C318" s="1">
         <v>5</v>
       </c>
-      <c r="C318" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D318" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E318" s="1">
         <v>22</v>
@@ -9515,14 +9515,14 @@
       <c r="A319" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B319" s="1">
-        <v>6</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>13</v>
+      <c r="B319" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C319" s="1">
+        <v>6</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E319" s="1">
         <v>22.6</v>
@@ -9532,14 +9532,14 @@
       <c r="A320" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B320" s="1">
-        <v>0</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>13</v>
+      <c r="B320" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C320" s="1">
+        <v>0</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E320" s="1">
         <v>24.8</v>
@@ -9549,14 +9549,14 @@
       <c r="A321" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B321" s="1">
+      <c r="B321" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C321" s="1">
         <v>1</v>
       </c>
-      <c r="C321" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D321" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E321" s="1">
         <v>26.2</v>
@@ -9566,14 +9566,14 @@
       <c r="A322" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B322" s="1">
+      <c r="B322" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C322" s="1">
         <v>2</v>
       </c>
-      <c r="C322" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D322" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E322" s="1">
         <v>30.8</v>
@@ -9583,14 +9583,14 @@
       <c r="A323" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B323" s="1">
+      <c r="B323" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C323" s="1">
         <v>3</v>
       </c>
-      <c r="C323" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D323" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E323" s="1">
         <v>31.3</v>
@@ -9600,14 +9600,14 @@
       <c r="A324" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B324" s="1">
+      <c r="B324" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C324" s="1">
         <v>4</v>
       </c>
-      <c r="C324" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D324" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E324" s="1">
         <v>32.5</v>
@@ -9617,14 +9617,14 @@
       <c r="A325" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B325" s="1">
+      <c r="B325" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C325" s="1">
         <v>5</v>
       </c>
-      <c r="C325" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D325" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E325" s="1">
         <v>32</v>
@@ -9634,14 +9634,14 @@
       <c r="A326" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B326" s="1">
-        <v>6</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>13</v>
+      <c r="B326" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C326" s="1">
+        <v>6</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E326" s="1">
         <v>34.200000000000003</v>
@@ -9651,14 +9651,14 @@
       <c r="A327" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B327" s="1">
-        <v>0</v>
-      </c>
-      <c r="C327" s="1" t="s">
-        <v>13</v>
+      <c r="B327" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C327" s="1">
+        <v>0</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E327" s="1">
         <v>23</v>
@@ -9668,14 +9668,14 @@
       <c r="A328" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B328" s="1">
+      <c r="B328" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C328" s="1">
         <v>1</v>
       </c>
-      <c r="C328" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D328" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E328" s="1">
         <v>25.4</v>
@@ -9685,14 +9685,14 @@
       <c r="A329" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B329" s="1">
+      <c r="B329" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C329" s="1">
         <v>2</v>
       </c>
-      <c r="C329" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D329" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E329" s="1">
         <v>28.2</v>
@@ -9702,14 +9702,14 @@
       <c r="A330" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B330" s="1">
+      <c r="B330" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C330" s="1">
         <v>3</v>
       </c>
-      <c r="C330" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D330" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E330" s="1">
         <v>28.2</v>
@@ -9719,14 +9719,14 @@
       <c r="A331" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B331" s="1">
+      <c r="B331" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C331" s="1">
         <v>4</v>
       </c>
-      <c r="C331" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D331" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E331" s="1">
         <v>29.5</v>
@@ -9736,14 +9736,14 @@
       <c r="A332" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B332" s="1">
+      <c r="B332" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C332" s="1">
         <v>5</v>
       </c>
-      <c r="C332" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D332" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E332" s="1">
         <v>30.9</v>
@@ -9753,14 +9753,14 @@
       <c r="A333" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B333" s="1">
-        <v>6</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>13</v>
+      <c r="B333" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C333" s="1">
+        <v>6</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E333" s="1">
         <v>30.8</v>
@@ -9770,14 +9770,14 @@
       <c r="A334" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B334" s="1">
-        <v>0</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>13</v>
+      <c r="B334" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C334" s="1">
+        <v>0</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E334" s="1">
         <v>23.4</v>
@@ -9787,14 +9787,14 @@
       <c r="A335" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B335" s="1">
+      <c r="B335" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C335" s="1">
         <v>1</v>
       </c>
-      <c r="C335" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D335" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E335" s="1">
         <v>25.2</v>
@@ -9804,14 +9804,14 @@
       <c r="A336" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B336" s="1">
+      <c r="B336" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C336" s="1">
         <v>2</v>
       </c>
-      <c r="C336" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D336" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E336" s="1">
         <v>27.4</v>
@@ -9821,14 +9821,14 @@
       <c r="A337" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B337" s="1">
+      <c r="B337" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C337" s="1">
         <v>3</v>
       </c>
-      <c r="C337" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D337" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E337" s="1">
         <v>28.8</v>
@@ -9838,14 +9838,14 @@
       <c r="A338" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B338" s="1">
+      <c r="B338" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C338" s="1">
         <v>4</v>
       </c>
-      <c r="C338" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D338" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E338" s="1">
         <v>28</v>
@@ -9855,14 +9855,14 @@
       <c r="A339" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B339" s="1">
+      <c r="B339" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C339" s="1">
         <v>5</v>
       </c>
-      <c r="C339" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D339" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E339" s="1">
         <v>28.8</v>
@@ -9872,14 +9872,14 @@
       <c r="A340" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B340" s="1">
-        <v>6</v>
-      </c>
-      <c r="C340" s="1" t="s">
-        <v>13</v>
+      <c r="B340" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C340" s="1">
+        <v>6</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E340" s="1">
         <v>29.9</v>
@@ -9889,14 +9889,14 @@
       <c r="A341" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B341" s="1">
-        <v>0</v>
-      </c>
-      <c r="C341" s="1" t="s">
-        <v>13</v>
+      <c r="B341" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C341" s="1">
+        <v>0</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E341" s="1">
         <v>26</v>
@@ -9906,14 +9906,14 @@
       <c r="A342" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B342" s="1">
+      <c r="B342" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C342" s="1">
         <v>1</v>
       </c>
-      <c r="C342" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D342" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E342" s="1">
         <v>28.1</v>
@@ -9923,14 +9923,14 @@
       <c r="A343" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B343" s="1">
+      <c r="B343" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C343" s="1">
         <v>2</v>
       </c>
-      <c r="C343" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D343" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E343" s="1">
         <v>30.6</v>
@@ -9940,14 +9940,14 @@
       <c r="A344" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B344" s="1">
+      <c r="B344" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C344" s="1">
         <v>3</v>
       </c>
-      <c r="C344" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D344" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E344" s="1">
         <v>31.7</v>
@@ -9957,14 +9957,14 @@
       <c r="A345" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B345" s="1">
+      <c r="B345" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C345" s="1">
         <v>4</v>
       </c>
-      <c r="C345" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D345" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E345" s="1">
         <v>32</v>
@@ -9974,14 +9974,14 @@
       <c r="A346" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B346" s="1">
+      <c r="B346" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C346" s="1">
         <v>5</v>
       </c>
-      <c r="C346" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D346" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E346" s="1">
         <v>33.700000000000003</v>
@@ -9991,14 +9991,14 @@
       <c r="A347" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B347" s="1">
-        <v>6</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>13</v>
+      <c r="B347" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C347" s="1">
+        <v>6</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E347" s="1">
         <v>32.799999999999997</v>
@@ -10008,14 +10008,14 @@
       <c r="A348" t="s">
         <v>64</v>
       </c>
-      <c r="B348">
-        <v>0</v>
-      </c>
-      <c r="C348" t="s">
-        <v>13</v>
+      <c r="B348" t="s">
+        <v>6</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
       </c>
       <c r="D348" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E348">
         <v>24.7</v>
@@ -10025,14 +10025,14 @@
       <c r="A349" t="s">
         <v>64</v>
       </c>
-      <c r="B349">
+      <c r="B349" t="s">
+        <v>6</v>
+      </c>
+      <c r="C349">
         <v>1</v>
       </c>
-      <c r="C349" t="s">
-        <v>13</v>
-      </c>
       <c r="D349" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E349">
         <v>28.3</v>
@@ -10042,14 +10042,14 @@
       <c r="A350" t="s">
         <v>64</v>
       </c>
-      <c r="B350">
+      <c r="B350" t="s">
+        <v>6</v>
+      </c>
+      <c r="C350">
         <v>2</v>
       </c>
-      <c r="C350" t="s">
-        <v>13</v>
-      </c>
       <c r="D350" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E350">
         <v>29.3</v>
@@ -10059,14 +10059,14 @@
       <c r="A351" t="s">
         <v>64</v>
       </c>
-      <c r="B351">
+      <c r="B351" t="s">
+        <v>6</v>
+      </c>
+      <c r="C351">
         <v>3</v>
       </c>
-      <c r="C351" t="s">
-        <v>13</v>
-      </c>
       <c r="D351" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E351">
         <v>31</v>
@@ -10076,14 +10076,14 @@
       <c r="A352" t="s">
         <v>64</v>
       </c>
-      <c r="B352">
+      <c r="B352" t="s">
+        <v>6</v>
+      </c>
+      <c r="C352">
         <v>4</v>
       </c>
-      <c r="C352" t="s">
-        <v>13</v>
-      </c>
       <c r="D352" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E352">
         <v>31.3</v>
@@ -10093,14 +10093,14 @@
       <c r="A353" t="s">
         <v>64</v>
       </c>
-      <c r="B353">
+      <c r="B353" t="s">
+        <v>6</v>
+      </c>
+      <c r="C353">
         <v>5</v>
       </c>
-      <c r="C353" t="s">
-        <v>13</v>
-      </c>
       <c r="D353" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E353">
         <v>31.1</v>
@@ -10110,14 +10110,14 @@
       <c r="A354" t="s">
         <v>64</v>
       </c>
-      <c r="B354">
-        <v>6</v>
-      </c>
-      <c r="C354" t="s">
-        <v>13</v>
+      <c r="B354" t="s">
+        <v>6</v>
+      </c>
+      <c r="C354">
+        <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E354">
         <v>35.5</v>
@@ -10127,14 +10127,14 @@
       <c r="A355" t="s">
         <v>65</v>
       </c>
-      <c r="B355">
-        <v>0</v>
-      </c>
-      <c r="C355" t="s">
-        <v>13</v>
+      <c r="B355" t="s">
+        <v>6</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
       </c>
       <c r="D355" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E355">
         <v>26.6</v>
@@ -10144,14 +10144,14 @@
       <c r="A356" t="s">
         <v>65</v>
       </c>
-      <c r="B356">
+      <c r="B356" t="s">
+        <v>6</v>
+      </c>
+      <c r="C356">
         <v>1</v>
       </c>
-      <c r="C356" t="s">
-        <v>13</v>
-      </c>
       <c r="D356" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E356">
         <v>29.4</v>
@@ -10161,14 +10161,14 @@
       <c r="A357" t="s">
         <v>65</v>
       </c>
-      <c r="B357">
+      <c r="B357" t="s">
+        <v>6</v>
+      </c>
+      <c r="C357">
         <v>2</v>
       </c>
-      <c r="C357" t="s">
-        <v>13</v>
-      </c>
       <c r="D357" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E357">
         <v>29.1</v>
@@ -10178,14 +10178,14 @@
       <c r="A358" t="s">
         <v>65</v>
       </c>
-      <c r="B358">
+      <c r="B358" t="s">
+        <v>6</v>
+      </c>
+      <c r="C358">
         <v>3</v>
       </c>
-      <c r="C358" t="s">
-        <v>13</v>
-      </c>
       <c r="D358" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E358">
         <v>31</v>
@@ -10195,14 +10195,14 @@
       <c r="A359" t="s">
         <v>65</v>
       </c>
-      <c r="B359">
+      <c r="B359" t="s">
+        <v>6</v>
+      </c>
+      <c r="C359">
         <v>4</v>
       </c>
-      <c r="C359" t="s">
-        <v>13</v>
-      </c>
       <c r="D359" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E359">
         <v>30.8</v>
@@ -10212,14 +10212,14 @@
       <c r="A360" t="s">
         <v>65</v>
       </c>
-      <c r="B360">
+      <c r="B360" t="s">
+        <v>6</v>
+      </c>
+      <c r="C360">
         <v>5</v>
       </c>
-      <c r="C360" t="s">
-        <v>13</v>
-      </c>
       <c r="D360" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E360">
         <v>30.2</v>
@@ -10229,14 +10229,14 @@
       <c r="A361" t="s">
         <v>65</v>
       </c>
-      <c r="B361">
-        <v>6</v>
-      </c>
-      <c r="C361" t="s">
-        <v>13</v>
+      <c r="B361" t="s">
+        <v>6</v>
+      </c>
+      <c r="C361">
+        <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E361">
         <v>31.3</v>
@@ -10246,14 +10246,14 @@
       <c r="A362" t="s">
         <v>66</v>
       </c>
-      <c r="B362">
-        <v>0</v>
-      </c>
-      <c r="C362" t="s">
-        <v>13</v>
+      <c r="B362" t="s">
+        <v>6</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
       </c>
       <c r="D362" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E362">
         <v>26.9</v>
@@ -10263,14 +10263,14 @@
       <c r="A363" t="s">
         <v>66</v>
       </c>
-      <c r="B363">
+      <c r="B363" t="s">
+        <v>6</v>
+      </c>
+      <c r="C363">
         <v>1</v>
       </c>
-      <c r="C363" t="s">
-        <v>13</v>
-      </c>
       <c r="D363" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E363">
         <v>29.3</v>
@@ -10280,14 +10280,14 @@
       <c r="A364" t="s">
         <v>66</v>
       </c>
-      <c r="B364">
+      <c r="B364" t="s">
+        <v>6</v>
+      </c>
+      <c r="C364">
         <v>2</v>
       </c>
-      <c r="C364" t="s">
-        <v>13</v>
-      </c>
       <c r="D364" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E364">
         <v>29.9</v>
@@ -10297,14 +10297,14 @@
       <c r="A365" t="s">
         <v>66</v>
       </c>
-      <c r="B365">
+      <c r="B365" t="s">
+        <v>6</v>
+      </c>
+      <c r="C365">
         <v>3</v>
       </c>
-      <c r="C365" t="s">
-        <v>13</v>
-      </c>
       <c r="D365" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E365">
         <v>30.8</v>
@@ -10314,14 +10314,14 @@
       <c r="A366" t="s">
         <v>67</v>
       </c>
-      <c r="B366">
-        <v>0</v>
-      </c>
-      <c r="C366" t="s">
-        <v>13</v>
+      <c r="B366" t="s">
+        <v>6</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
       </c>
       <c r="D366" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E366">
         <v>26.9</v>
@@ -10331,14 +10331,14 @@
       <c r="A367" t="s">
         <v>67</v>
       </c>
-      <c r="B367">
+      <c r="B367" t="s">
+        <v>6</v>
+      </c>
+      <c r="C367">
         <v>1</v>
       </c>
-      <c r="C367" t="s">
-        <v>13</v>
-      </c>
       <c r="D367" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E367">
         <v>29.3</v>
@@ -10348,14 +10348,14 @@
       <c r="A368" t="s">
         <v>67</v>
       </c>
-      <c r="B368">
+      <c r="B368" t="s">
+        <v>6</v>
+      </c>
+      <c r="C368">
         <v>2</v>
       </c>
-      <c r="C368" t="s">
-        <v>13</v>
-      </c>
       <c r="D368" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E368">
         <v>29.9</v>
@@ -10365,14 +10365,14 @@
       <c r="A369" t="s">
         <v>67</v>
       </c>
-      <c r="B369">
+      <c r="B369" t="s">
+        <v>6</v>
+      </c>
+      <c r="C369">
         <v>3</v>
       </c>
-      <c r="C369" t="s">
-        <v>13</v>
-      </c>
       <c r="D369" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E369">
         <v>29.9</v>
@@ -10382,14 +10382,14 @@
       <c r="A370" t="s">
         <v>67</v>
       </c>
-      <c r="B370">
+      <c r="B370" t="s">
+        <v>6</v>
+      </c>
+      <c r="C370">
         <v>4</v>
       </c>
-      <c r="C370" t="s">
-        <v>13</v>
-      </c>
       <c r="D370" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E370">
         <v>31.9</v>
@@ -10399,14 +10399,14 @@
       <c r="A371" t="s">
         <v>67</v>
       </c>
-      <c r="B371">
+      <c r="B371" t="s">
+        <v>6</v>
+      </c>
+      <c r="C371">
         <v>5</v>
       </c>
-      <c r="C371" t="s">
-        <v>13</v>
-      </c>
       <c r="D371" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E371">
         <v>34.299999999999997</v>
@@ -10416,14 +10416,14 @@
       <c r="A372" t="s">
         <v>67</v>
       </c>
-      <c r="B372">
-        <v>6</v>
-      </c>
-      <c r="C372" t="s">
-        <v>13</v>
+      <c r="B372" t="s">
+        <v>6</v>
+      </c>
+      <c r="C372">
+        <v>6</v>
       </c>
       <c r="D372" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E372">
         <v>35</v>
@@ -10433,14 +10433,14 @@
       <c r="A373" t="s">
         <v>68</v>
       </c>
-      <c r="B373">
-        <v>0</v>
-      </c>
-      <c r="C373" t="s">
-        <v>13</v>
+      <c r="B373" t="s">
+        <v>25</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
       </c>
       <c r="D373" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E373">
         <v>27</v>
@@ -10450,14 +10450,14 @@
       <c r="A374" t="s">
         <v>68</v>
       </c>
-      <c r="B374">
+      <c r="B374" t="s">
+        <v>25</v>
+      </c>
+      <c r="C374">
         <v>1</v>
       </c>
-      <c r="C374" t="s">
-        <v>13</v>
-      </c>
       <c r="D374" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E374">
         <v>26.9</v>
@@ -10467,14 +10467,14 @@
       <c r="A375" t="s">
         <v>68</v>
       </c>
-      <c r="B375">
+      <c r="B375" t="s">
+        <v>25</v>
+      </c>
+      <c r="C375">
         <v>2</v>
       </c>
-      <c r="C375" t="s">
-        <v>13</v>
-      </c>
       <c r="D375" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E375">
         <v>26</v>
@@ -10484,14 +10484,14 @@
       <c r="A376" t="s">
         <v>68</v>
       </c>
-      <c r="B376">
+      <c r="B376" t="s">
+        <v>25</v>
+      </c>
+      <c r="C376">
         <v>3</v>
       </c>
-      <c r="C376" t="s">
-        <v>13</v>
-      </c>
       <c r="D376" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E376">
         <v>26.9</v>
@@ -10501,14 +10501,14 @@
       <c r="A377" t="s">
         <v>68</v>
       </c>
-      <c r="B377">
+      <c r="B377" t="s">
+        <v>25</v>
+      </c>
+      <c r="C377">
         <v>4</v>
       </c>
-      <c r="C377" t="s">
-        <v>13</v>
-      </c>
       <c r="D377" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E377">
         <v>25.7</v>
@@ -10518,14 +10518,14 @@
       <c r="A378" t="s">
         <v>68</v>
       </c>
-      <c r="B378">
+      <c r="B378" t="s">
+        <v>25</v>
+      </c>
+      <c r="C378">
         <v>5</v>
       </c>
-      <c r="C378" t="s">
-        <v>13</v>
-      </c>
       <c r="D378" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E378">
         <v>25.7</v>
@@ -10535,14 +10535,14 @@
       <c r="A379" t="s">
         <v>68</v>
       </c>
-      <c r="B379">
-        <v>6</v>
-      </c>
-      <c r="C379" t="s">
-        <v>13</v>
+      <c r="B379" t="s">
+        <v>25</v>
+      </c>
+      <c r="C379">
+        <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E379">
         <v>27</v>
@@ -10552,14 +10552,14 @@
       <c r="A380" t="s">
         <v>69</v>
       </c>
-      <c r="B380">
-        <v>0</v>
-      </c>
-      <c r="C380" t="s">
-        <v>13</v>
+      <c r="B380" t="s">
+        <v>25</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
       </c>
       <c r="D380" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E380">
         <v>26.5</v>
@@ -10569,14 +10569,14 @@
       <c r="A381" t="s">
         <v>69</v>
       </c>
-      <c r="B381">
+      <c r="B381" t="s">
+        <v>25</v>
+      </c>
+      <c r="C381">
         <v>1</v>
       </c>
-      <c r="C381" t="s">
-        <v>13</v>
-      </c>
       <c r="D381" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E381">
         <v>28.5</v>
@@ -10586,14 +10586,14 @@
       <c r="A382" t="s">
         <v>69</v>
       </c>
-      <c r="B382">
+      <c r="B382" t="s">
+        <v>25</v>
+      </c>
+      <c r="C382">
         <v>2</v>
       </c>
-      <c r="C382" t="s">
-        <v>13</v>
-      </c>
       <c r="D382" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E382">
         <v>29</v>
@@ -10603,14 +10603,14 @@
       <c r="A383" t="s">
         <v>69</v>
       </c>
-      <c r="B383">
+      <c r="B383" t="s">
+        <v>25</v>
+      </c>
+      <c r="C383">
         <v>3</v>
       </c>
-      <c r="C383" t="s">
-        <v>13</v>
-      </c>
       <c r="D383" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E383">
         <v>28.5</v>
@@ -10620,14 +10620,14 @@
       <c r="A384" t="s">
         <v>69</v>
       </c>
-      <c r="B384">
+      <c r="B384" t="s">
+        <v>25</v>
+      </c>
+      <c r="C384">
         <v>4</v>
       </c>
-      <c r="C384" t="s">
-        <v>13</v>
-      </c>
       <c r="D384" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E384">
         <v>28.5</v>
@@ -10637,14 +10637,14 @@
       <c r="A385" t="s">
         <v>69</v>
       </c>
-      <c r="B385">
+      <c r="B385" t="s">
+        <v>25</v>
+      </c>
+      <c r="C385">
         <v>5</v>
       </c>
-      <c r="C385" t="s">
-        <v>13</v>
-      </c>
       <c r="D385" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E385">
         <v>28.5</v>
@@ -10654,14 +10654,14 @@
       <c r="A386" t="s">
         <v>69</v>
       </c>
-      <c r="B386">
-        <v>6</v>
-      </c>
-      <c r="C386" t="s">
-        <v>13</v>
+      <c r="B386" t="s">
+        <v>25</v>
+      </c>
+      <c r="C386">
+        <v>6</v>
       </c>
       <c r="D386" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E386">
         <v>29.1</v>
@@ -10671,14 +10671,14 @@
       <c r="A387" t="s">
         <v>70</v>
       </c>
-      <c r="B387">
-        <v>0</v>
-      </c>
-      <c r="C387" t="s">
-        <v>13</v>
+      <c r="B387" t="s">
+        <v>25</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
       </c>
       <c r="D387" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E387">
         <v>28.9</v>
@@ -10688,14 +10688,14 @@
       <c r="A388" t="s">
         <v>70</v>
       </c>
-      <c r="B388">
+      <c r="B388" t="s">
+        <v>25</v>
+      </c>
+      <c r="C388">
         <v>1</v>
       </c>
-      <c r="C388" t="s">
-        <v>13</v>
-      </c>
       <c r="D388" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E388">
         <v>27.3</v>
@@ -10705,14 +10705,14 @@
       <c r="A389" t="s">
         <v>70</v>
       </c>
-      <c r="B389">
+      <c r="B389" t="s">
+        <v>25</v>
+      </c>
+      <c r="C389">
         <v>2</v>
       </c>
-      <c r="C389" t="s">
-        <v>13</v>
-      </c>
       <c r="D389" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E389">
         <v>29</v>
@@ -10722,14 +10722,14 @@
       <c r="A390" t="s">
         <v>70</v>
       </c>
-      <c r="B390">
+      <c r="B390" t="s">
+        <v>25</v>
+      </c>
+      <c r="C390">
         <v>3</v>
       </c>
-      <c r="C390" t="s">
-        <v>13</v>
-      </c>
       <c r="D390" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E390">
         <v>27.3</v>
@@ -10739,14 +10739,14 @@
       <c r="A391" t="s">
         <v>70</v>
       </c>
-      <c r="B391">
+      <c r="B391" t="s">
+        <v>25</v>
+      </c>
+      <c r="C391">
         <v>4</v>
       </c>
-      <c r="C391" t="s">
-        <v>13</v>
-      </c>
       <c r="D391" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E391">
         <v>29.3</v>
@@ -10756,14 +10756,14 @@
       <c r="A392" t="s">
         <v>70</v>
       </c>
-      <c r="B392">
+      <c r="B392" t="s">
+        <v>25</v>
+      </c>
+      <c r="C392">
         <v>5</v>
       </c>
-      <c r="C392" t="s">
-        <v>13</v>
-      </c>
       <c r="D392" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E392">
         <v>29.3</v>
@@ -10773,14 +10773,14 @@
       <c r="A393" t="s">
         <v>70</v>
       </c>
-      <c r="B393">
-        <v>6</v>
-      </c>
-      <c r="C393" t="s">
-        <v>13</v>
+      <c r="B393" t="s">
+        <v>25</v>
+      </c>
+      <c r="C393">
+        <v>6</v>
       </c>
       <c r="D393" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E393">
         <v>27</v>
@@ -10790,14 +10790,14 @@
       <c r="A394" t="s">
         <v>71</v>
       </c>
-      <c r="B394">
-        <v>0</v>
-      </c>
-      <c r="C394" t="s">
-        <v>13</v>
+      <c r="B394" t="s">
+        <v>6</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
       </c>
       <c r="D394" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E394">
         <v>22.5</v>
@@ -10807,14 +10807,14 @@
       <c r="A395" t="s">
         <v>71</v>
       </c>
-      <c r="B395">
+      <c r="B395" t="s">
+        <v>6</v>
+      </c>
+      <c r="C395">
         <v>1</v>
       </c>
-      <c r="C395" t="s">
-        <v>13</v>
-      </c>
       <c r="D395" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E395">
         <v>32.9</v>
@@ -10824,14 +10824,14 @@
       <c r="A396" t="s">
         <v>71</v>
       </c>
-      <c r="B396">
+      <c r="B396" t="s">
+        <v>6</v>
+      </c>
+      <c r="C396">
         <v>2</v>
       </c>
-      <c r="C396" t="s">
-        <v>13</v>
-      </c>
       <c r="D396" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E396">
         <v>28</v>
@@ -10841,14 +10841,14 @@
       <c r="A397" t="s">
         <v>71</v>
       </c>
-      <c r="B397">
+      <c r="B397" t="s">
+        <v>6</v>
+      </c>
+      <c r="C397">
         <v>3</v>
       </c>
-      <c r="C397" t="s">
-        <v>13</v>
-      </c>
       <c r="D397" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E397">
         <v>32.200000000000003</v>
@@ -10858,14 +10858,14 @@
       <c r="A398" t="s">
         <v>71</v>
       </c>
-      <c r="B398">
+      <c r="B398" t="s">
+        <v>6</v>
+      </c>
+      <c r="C398">
         <v>4</v>
       </c>
-      <c r="C398" t="s">
-        <v>13</v>
-      </c>
       <c r="D398" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E398">
         <v>31.1</v>
@@ -10875,14 +10875,14 @@
       <c r="A399" t="s">
         <v>71</v>
       </c>
-      <c r="B399">
+      <c r="B399" t="s">
+        <v>6</v>
+      </c>
+      <c r="C399">
         <v>5</v>
       </c>
-      <c r="C399" t="s">
-        <v>13</v>
-      </c>
       <c r="D399" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E399">
         <v>35</v>
@@ -10892,14 +10892,14 @@
       <c r="A400" t="s">
         <v>71</v>
       </c>
-      <c r="B400">
+      <c r="B400" t="s">
+        <v>6</v>
+      </c>
+      <c r="C400">
         <v>5</v>
       </c>
-      <c r="C400" t="s">
-        <v>13</v>
-      </c>
       <c r="D400" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E400">
         <v>35</v>
@@ -10909,14 +10909,14 @@
       <c r="A401" t="s">
         <v>71</v>
       </c>
-      <c r="B401">
-        <v>6</v>
-      </c>
-      <c r="C401" t="s">
-        <v>13</v>
+      <c r="B401" t="s">
+        <v>6</v>
+      </c>
+      <c r="C401">
+        <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E401">
         <v>38.200000000000003</v>
@@ -10926,14 +10926,14 @@
       <c r="A402" t="s">
         <v>72</v>
       </c>
-      <c r="B402">
-        <v>0</v>
-      </c>
-      <c r="C402" t="s">
-        <v>13</v>
+      <c r="B402" t="s">
+        <v>6</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
       </c>
       <c r="D402" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E402">
         <v>26.4</v>
@@ -10943,14 +10943,14 @@
       <c r="A403" t="s">
         <v>72</v>
       </c>
-      <c r="B403">
+      <c r="B403" t="s">
+        <v>6</v>
+      </c>
+      <c r="C403">
         <v>1</v>
       </c>
-      <c r="C403" t="s">
-        <v>13</v>
-      </c>
       <c r="D403" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E403">
         <v>31</v>
@@ -10960,14 +10960,14 @@
       <c r="A404" t="s">
         <v>72</v>
       </c>
-      <c r="B404">
+      <c r="B404" t="s">
+        <v>6</v>
+      </c>
+      <c r="C404">
         <v>2</v>
       </c>
-      <c r="C404" t="s">
-        <v>13</v>
-      </c>
       <c r="D404" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E404">
         <v>36.700000000000003</v>
@@ -10977,14 +10977,14 @@
       <c r="A405" t="s">
         <v>72</v>
       </c>
-      <c r="B405">
+      <c r="B405" t="s">
+        <v>6</v>
+      </c>
+      <c r="C405">
         <v>3</v>
       </c>
-      <c r="C405" t="s">
-        <v>13</v>
-      </c>
       <c r="D405" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E405">
         <v>38</v>
@@ -10994,14 +10994,14 @@
       <c r="A406" t="s">
         <v>72</v>
       </c>
-      <c r="B406">
+      <c r="B406" t="s">
+        <v>6</v>
+      </c>
+      <c r="C406">
         <v>4</v>
       </c>
-      <c r="C406" t="s">
-        <v>13</v>
-      </c>
       <c r="D406" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E406">
         <v>38.799999999999997</v>
@@ -11011,14 +11011,14 @@
       <c r="A407" t="s">
         <v>72</v>
       </c>
-      <c r="B407">
+      <c r="B407" t="s">
+        <v>6</v>
+      </c>
+      <c r="C407">
         <v>5</v>
       </c>
-      <c r="C407" t="s">
-        <v>13</v>
-      </c>
       <c r="D407" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E407">
         <v>42.5</v>
@@ -11028,14 +11028,14 @@
       <c r="A408" t="s">
         <v>72</v>
       </c>
-      <c r="B408">
+      <c r="B408" t="s">
+        <v>6</v>
+      </c>
+      <c r="C408">
         <v>5</v>
       </c>
-      <c r="C408" t="s">
-        <v>13</v>
-      </c>
       <c r="D408" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E408">
         <v>42.5</v>
@@ -11045,14 +11045,14 @@
       <c r="A409" t="s">
         <v>72</v>
       </c>
-      <c r="B409">
-        <v>6</v>
-      </c>
-      <c r="C409" t="s">
-        <v>13</v>
+      <c r="B409" t="s">
+        <v>6</v>
+      </c>
+      <c r="C409">
+        <v>6</v>
       </c>
       <c r="D409" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E409">
         <v>44.3</v>
@@ -11062,14 +11062,14 @@
       <c r="A410" t="s">
         <v>73</v>
       </c>
-      <c r="B410">
-        <v>0</v>
-      </c>
-      <c r="C410" t="s">
-        <v>13</v>
+      <c r="B410" t="s">
+        <v>6</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
       </c>
       <c r="D410" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E410">
         <v>24.2</v>
@@ -11079,14 +11079,14 @@
       <c r="A411" t="s">
         <v>73</v>
       </c>
-      <c r="B411">
+      <c r="B411" t="s">
+        <v>6</v>
+      </c>
+      <c r="C411">
         <v>1</v>
       </c>
-      <c r="C411" t="s">
-        <v>13</v>
-      </c>
       <c r="D411" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E411">
         <v>34</v>
@@ -11096,14 +11096,14 @@
       <c r="A412" t="s">
         <v>73</v>
       </c>
-      <c r="B412">
+      <c r="B412" t="s">
+        <v>6</v>
+      </c>
+      <c r="C412">
         <v>2</v>
       </c>
-      <c r="C412" t="s">
-        <v>13</v>
-      </c>
       <c r="D412" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E412">
         <v>30.4</v>
@@ -11113,14 +11113,14 @@
       <c r="A413" t="s">
         <v>73</v>
       </c>
-      <c r="B413">
+      <c r="B413" t="s">
+        <v>6</v>
+      </c>
+      <c r="C413">
         <v>3</v>
       </c>
-      <c r="C413" t="s">
-        <v>13</v>
-      </c>
       <c r="D413" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E413">
         <v>30</v>
@@ -11130,14 +11130,14 @@
       <c r="A414" t="s">
         <v>73</v>
       </c>
-      <c r="B414">
+      <c r="B414" t="s">
+        <v>6</v>
+      </c>
+      <c r="C414">
         <v>4</v>
       </c>
-      <c r="C414" t="s">
-        <v>13</v>
-      </c>
       <c r="D414" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E414">
         <v>32.200000000000003</v>
@@ -11147,14 +11147,14 @@
       <c r="A415" t="s">
         <v>73</v>
       </c>
-      <c r="B415">
+      <c r="B415" t="s">
+        <v>6</v>
+      </c>
+      <c r="C415">
         <v>5</v>
       </c>
-      <c r="C415" t="s">
-        <v>13</v>
-      </c>
       <c r="D415" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E415">
         <v>31.8</v>
@@ -11164,14 +11164,14 @@
       <c r="A416" t="s">
         <v>73</v>
       </c>
-      <c r="B416">
+      <c r="B416" t="s">
+        <v>6</v>
+      </c>
+      <c r="C416">
         <v>5</v>
       </c>
-      <c r="C416" t="s">
-        <v>13</v>
-      </c>
       <c r="D416" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E416">
         <v>31.8</v>
@@ -11181,14 +11181,14 @@
       <c r="A417" t="s">
         <v>73</v>
       </c>
-      <c r="B417">
-        <v>6</v>
-      </c>
-      <c r="C417" t="s">
-        <v>13</v>
+      <c r="B417" t="s">
+        <v>6</v>
+      </c>
+      <c r="C417">
+        <v>6</v>
       </c>
       <c r="D417" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E417">
         <v>33</v>
@@ -11198,14 +11198,14 @@
       <c r="A418" t="s">
         <v>74</v>
       </c>
-      <c r="B418">
-        <v>0</v>
-      </c>
-      <c r="C418" t="s">
-        <v>13</v>
+      <c r="B418" t="s">
+        <v>6</v>
+      </c>
+      <c r="C418">
+        <v>0</v>
       </c>
       <c r="D418" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E418">
         <v>26.3</v>
@@ -11215,14 +11215,14 @@
       <c r="A419" t="s">
         <v>74</v>
       </c>
-      <c r="B419">
+      <c r="B419" t="s">
+        <v>6</v>
+      </c>
+      <c r="C419">
         <v>1</v>
       </c>
-      <c r="C419" t="s">
-        <v>13</v>
-      </c>
       <c r="D419" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E419">
         <v>31.5</v>
@@ -11232,14 +11232,14 @@
       <c r="A420" t="s">
         <v>74</v>
       </c>
-      <c r="B420">
+      <c r="B420" t="s">
+        <v>6</v>
+      </c>
+      <c r="C420">
         <v>2</v>
       </c>
-      <c r="C420" t="s">
-        <v>13</v>
-      </c>
       <c r="D420" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E420">
         <v>29.8</v>
@@ -11249,14 +11249,14 @@
       <c r="A421" t="s">
         <v>74</v>
       </c>
-      <c r="B421">
+      <c r="B421" t="s">
+        <v>6</v>
+      </c>
+      <c r="C421">
         <v>3</v>
       </c>
-      <c r="C421" t="s">
-        <v>13</v>
-      </c>
       <c r="D421" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E421">
         <v>30.1</v>
@@ -11266,14 +11266,14 @@
       <c r="A422" t="s">
         <v>74</v>
       </c>
-      <c r="B422">
+      <c r="B422" t="s">
+        <v>6</v>
+      </c>
+      <c r="C422">
         <v>4</v>
       </c>
-      <c r="C422" t="s">
-        <v>13</v>
-      </c>
       <c r="D422" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E422">
         <v>31</v>
@@ -11283,14 +11283,14 @@
       <c r="A423" t="s">
         <v>74</v>
       </c>
-      <c r="B423">
+      <c r="B423" t="s">
+        <v>6</v>
+      </c>
+      <c r="C423">
         <v>5</v>
       </c>
-      <c r="C423" t="s">
-        <v>13</v>
-      </c>
       <c r="D423" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E423">
         <v>32.9</v>
@@ -11300,14 +11300,14 @@
       <c r="A424" t="s">
         <v>74</v>
       </c>
-      <c r="B424">
+      <c r="B424" t="s">
+        <v>6</v>
+      </c>
+      <c r="C424">
         <v>5</v>
       </c>
-      <c r="C424" t="s">
-        <v>13</v>
-      </c>
       <c r="D424" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E424">
         <v>32.9</v>
@@ -11317,14 +11317,14 @@
       <c r="A425" t="s">
         <v>74</v>
       </c>
-      <c r="B425">
-        <v>6</v>
-      </c>
-      <c r="C425" t="s">
-        <v>13</v>
+      <c r="B425" t="s">
+        <v>6</v>
+      </c>
+      <c r="C425">
+        <v>6</v>
       </c>
       <c r="D425" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E425">
         <v>35</v>
@@ -11334,14 +11334,14 @@
       <c r="A426" t="s">
         <v>75</v>
       </c>
-      <c r="B426">
-        <v>0</v>
-      </c>
-      <c r="C426" t="s">
-        <v>13</v>
+      <c r="B426" t="s">
+        <v>25</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
       </c>
       <c r="D426" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E426">
         <v>21.4</v>
@@ -11351,14 +11351,14 @@
       <c r="A427" t="s">
         <v>75</v>
       </c>
-      <c r="B427">
+      <c r="B427" t="s">
+        <v>25</v>
+      </c>
+      <c r="C427">
         <v>1</v>
       </c>
-      <c r="C427" t="s">
-        <v>13</v>
-      </c>
       <c r="D427" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E427">
         <v>21.4</v>
@@ -11368,14 +11368,14 @@
       <c r="A428" t="s">
         <v>75</v>
       </c>
-      <c r="B428">
+      <c r="B428" t="s">
+        <v>25</v>
+      </c>
+      <c r="C428">
         <v>2</v>
       </c>
-      <c r="C428" t="s">
-        <v>13</v>
-      </c>
       <c r="D428" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E428">
         <v>26.3</v>
@@ -11385,14 +11385,14 @@
       <c r="A429" t="s">
         <v>75</v>
       </c>
-      <c r="B429">
+      <c r="B429" t="s">
+        <v>25</v>
+      </c>
+      <c r="C429">
         <v>3</v>
       </c>
-      <c r="C429" t="s">
-        <v>13</v>
-      </c>
       <c r="D429" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E429">
         <v>28.5</v>
@@ -11402,14 +11402,14 @@
       <c r="A430" t="s">
         <v>75</v>
       </c>
-      <c r="B430">
+      <c r="B430" t="s">
+        <v>25</v>
+      </c>
+      <c r="C430">
         <v>4</v>
       </c>
-      <c r="C430" t="s">
-        <v>13</v>
-      </c>
       <c r="D430" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E430">
         <v>28.6</v>
@@ -11419,14 +11419,14 @@
       <c r="A431" t="s">
         <v>75</v>
       </c>
-      <c r="B431">
+      <c r="B431" t="s">
+        <v>25</v>
+      </c>
+      <c r="C431">
         <v>5</v>
       </c>
-      <c r="C431" t="s">
-        <v>13</v>
-      </c>
       <c r="D431" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E431">
         <v>25.5</v>
@@ -11436,14 +11436,14 @@
       <c r="A432" t="s">
         <v>75</v>
       </c>
-      <c r="B432">
-        <v>6</v>
-      </c>
-      <c r="C432" t="s">
-        <v>13</v>
+      <c r="B432" t="s">
+        <v>25</v>
+      </c>
+      <c r="C432">
+        <v>6</v>
       </c>
       <c r="D432" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E432">
         <v>25.7</v>
@@ -11453,14 +11453,14 @@
       <c r="A433" t="s">
         <v>76</v>
       </c>
-      <c r="B433">
-        <v>0</v>
-      </c>
-      <c r="C433" t="s">
-        <v>13</v>
+      <c r="B433" t="s">
+        <v>25</v>
+      </c>
+      <c r="C433">
+        <v>0</v>
       </c>
       <c r="D433" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E433">
         <v>22</v>
@@ -11470,14 +11470,14 @@
       <c r="A434" t="s">
         <v>76</v>
       </c>
-      <c r="B434">
+      <c r="B434" t="s">
+        <v>25</v>
+      </c>
+      <c r="C434">
         <v>1</v>
       </c>
-      <c r="C434" t="s">
-        <v>13</v>
-      </c>
       <c r="D434" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E434">
         <v>22</v>
@@ -11487,14 +11487,14 @@
       <c r="A435" t="s">
         <v>76</v>
       </c>
-      <c r="B435">
+      <c r="B435" t="s">
+        <v>25</v>
+      </c>
+      <c r="C435">
         <v>2</v>
       </c>
-      <c r="C435" t="s">
-        <v>13</v>
-      </c>
       <c r="D435" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E435">
         <v>27.6</v>
@@ -11504,14 +11504,14 @@
       <c r="A436" t="s">
         <v>76</v>
       </c>
-      <c r="B436">
+      <c r="B436" t="s">
+        <v>25</v>
+      </c>
+      <c r="C436">
         <v>3</v>
       </c>
-      <c r="C436" t="s">
-        <v>13</v>
-      </c>
       <c r="D436" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E436">
         <v>27.8</v>
@@ -11521,14 +11521,14 @@
       <c r="A437" t="s">
         <v>76</v>
       </c>
-      <c r="B437">
+      <c r="B437" t="s">
+        <v>25</v>
+      </c>
+      <c r="C437">
         <v>4</v>
       </c>
-      <c r="C437" t="s">
-        <v>13</v>
-      </c>
       <c r="D437" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E437">
         <v>26</v>
@@ -11538,14 +11538,14 @@
       <c r="A438" t="s">
         <v>76</v>
       </c>
-      <c r="B438">
+      <c r="B438" t="s">
+        <v>25</v>
+      </c>
+      <c r="C438">
         <v>5</v>
       </c>
-      <c r="C438" t="s">
-        <v>13</v>
-      </c>
       <c r="D438" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E438">
         <v>28.3</v>
@@ -11555,14 +11555,14 @@
       <c r="A439" t="s">
         <v>76</v>
       </c>
-      <c r="B439">
-        <v>6</v>
-      </c>
-      <c r="C439" t="s">
-        <v>13</v>
+      <c r="B439" t="s">
+        <v>25</v>
+      </c>
+      <c r="C439">
+        <v>6</v>
       </c>
       <c r="D439" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E439">
         <v>28.3</v>
@@ -11572,14 +11572,14 @@
       <c r="A440" t="s">
         <v>77</v>
       </c>
-      <c r="B440">
-        <v>0</v>
-      </c>
-      <c r="C440" t="s">
-        <v>13</v>
+      <c r="B440" t="s">
+        <v>25</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
       </c>
       <c r="D440" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E440">
         <v>26.5</v>
@@ -11589,14 +11589,14 @@
       <c r="A441" t="s">
         <v>77</v>
       </c>
-      <c r="B441">
+      <c r="B441" t="s">
+        <v>25</v>
+      </c>
+      <c r="C441">
         <v>1</v>
       </c>
-      <c r="C441" t="s">
-        <v>13</v>
-      </c>
       <c r="D441" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E441">
         <v>26.5</v>
@@ -11606,14 +11606,14 @@
       <c r="A442" t="s">
         <v>77</v>
       </c>
-      <c r="B442">
+      <c r="B442" t="s">
+        <v>25</v>
+      </c>
+      <c r="C442">
         <v>2</v>
       </c>
-      <c r="C442" t="s">
-        <v>13</v>
-      </c>
       <c r="D442" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E442">
         <v>26.5</v>
@@ -11623,14 +11623,14 @@
       <c r="A443" t="s">
         <v>77</v>
       </c>
-      <c r="B443">
+      <c r="B443" t="s">
+        <v>25</v>
+      </c>
+      <c r="C443">
         <v>3</v>
       </c>
-      <c r="C443" t="s">
-        <v>13</v>
-      </c>
       <c r="D443" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E443">
         <v>27.2</v>
@@ -11640,14 +11640,14 @@
       <c r="A444" t="s">
         <v>77</v>
       </c>
-      <c r="B444">
+      <c r="B444" t="s">
+        <v>25</v>
+      </c>
+      <c r="C444">
         <v>4</v>
       </c>
-      <c r="C444" t="s">
-        <v>13</v>
-      </c>
       <c r="D444" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E444">
         <v>27</v>
@@ -11657,14 +11657,14 @@
       <c r="A445" t="s">
         <v>77</v>
       </c>
-      <c r="B445">
+      <c r="B445" t="s">
+        <v>25</v>
+      </c>
+      <c r="C445">
         <v>5</v>
       </c>
-      <c r="C445" t="s">
-        <v>13</v>
-      </c>
       <c r="D445" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E445">
         <v>27.7</v>
@@ -11674,14 +11674,14 @@
       <c r="A446" t="s">
         <v>77</v>
       </c>
-      <c r="B446">
-        <v>6</v>
-      </c>
-      <c r="C446" t="s">
-        <v>13</v>
+      <c r="B446" t="s">
+        <v>25</v>
+      </c>
+      <c r="C446">
+        <v>6</v>
       </c>
       <c r="D446" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E446">
         <v>26.5</v>
@@ -11691,14 +11691,14 @@
       <c r="A447" t="s">
         <v>78</v>
       </c>
-      <c r="B447">
-        <v>0</v>
-      </c>
-      <c r="C447" t="s">
-        <v>13</v>
+      <c r="B447" t="s">
+        <v>25</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
       </c>
       <c r="D447" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E447">
         <v>26.3</v>
@@ -11708,14 +11708,14 @@
       <c r="A448" t="s">
         <v>78</v>
       </c>
-      <c r="B448">
+      <c r="B448" t="s">
+        <v>25</v>
+      </c>
+      <c r="C448">
         <v>1</v>
       </c>
-      <c r="C448" t="s">
-        <v>13</v>
-      </c>
       <c r="D448" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E448">
         <v>26.3</v>
@@ -11725,14 +11725,14 @@
       <c r="A449" t="s">
         <v>78</v>
       </c>
-      <c r="B449">
+      <c r="B449" t="s">
+        <v>25</v>
+      </c>
+      <c r="C449">
         <v>2</v>
       </c>
-      <c r="C449" t="s">
-        <v>13</v>
-      </c>
       <c r="D449" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E449">
         <v>26.3</v>
@@ -11742,14 +11742,14 @@
       <c r="A450" t="s">
         <v>78</v>
       </c>
-      <c r="B450">
+      <c r="B450" t="s">
+        <v>25</v>
+      </c>
+      <c r="C450">
         <v>3</v>
       </c>
-      <c r="C450" t="s">
-        <v>13</v>
-      </c>
       <c r="D450" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E450">
         <v>25.5</v>
@@ -11759,14 +11759,14 @@
       <c r="A451" t="s">
         <v>78</v>
       </c>
-      <c r="B451">
+      <c r="B451" t="s">
+        <v>25</v>
+      </c>
+      <c r="C451">
         <v>4</v>
       </c>
-      <c r="C451" t="s">
-        <v>13</v>
-      </c>
       <c r="D451" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E451">
         <v>25.8</v>
@@ -11776,14 +11776,14 @@
       <c r="A452" t="s">
         <v>78</v>
       </c>
-      <c r="B452">
+      <c r="B452" t="s">
+        <v>25</v>
+      </c>
+      <c r="C452">
         <v>5</v>
       </c>
-      <c r="C452" t="s">
-        <v>13</v>
-      </c>
       <c r="D452" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E452">
         <v>26</v>
@@ -11793,14 +11793,14 @@
       <c r="A453" t="s">
         <v>78</v>
       </c>
-      <c r="B453">
-        <v>6</v>
-      </c>
-      <c r="C453" t="s">
-        <v>13</v>
+      <c r="B453" t="s">
+        <v>25</v>
+      </c>
+      <c r="C453">
+        <v>6</v>
       </c>
       <c r="D453" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E453">
         <v>26</v>
